--- a/San_Jose_Apartments_Tracker.xlsx
+++ b/San_Jose_Apartments_Tracker.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="All Apartments (30)" sheetId="1" r:id="rId1"/>
+    <sheet name="All Apartments (91)" sheetId="1" r:id="rId1"/>
     <sheet name="Top Picks &amp; Sub-$3000" sheetId="2" r:id="rId2"/>
     <sheet name="Santa Clara SVP Zone" sheetId="3" r:id="rId3"/>
   </sheets>
@@ -102,7 +102,7 @@
     <col min="17" max="20" width="13" customWidth="1"/>
     <col min="21" max="21" width="28" customWidth="1"/>
     <col min="22" max="23" width="46" customWidth="1"/>
-    <col min="24" max="25" width="36" customWidth="1"/>
+    <col min="24" max="26" width="38" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -228,6 +228,11 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>Apartments.com Listing</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>Official Website</t>
         </is>
       </c>
@@ -337,6 +342,11 @@
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/north-park-apartment-homes-san-jose-ca/fsbvjbs/</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
           <t>https://www.irvinecompanyapartments.com/locations/northern-california/san-jose/north-park.html</t>
         </is>
       </c>
@@ -446,6 +456,11 @@
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/crescent-village-apartment-homes-san-jose-ca/kb57kc8/</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
           <t>https://www.irvinecompanyapartments.com/locations/northern-california/san-jose/crescent-village.html</t>
         </is>
       </c>
@@ -555,6 +570,11 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/enso-san-jose-ca/e5b3e4m/</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/san-jose/enso</t>
         </is>
       </c>
@@ -664,7 +684,12 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>https://www.aireliving.com/</t>
+          <t>https://www.apartments.com/aire-san-jose-ca/nrsnnzq/</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>https://aireliving.com/</t>
         </is>
       </c>
     </row>
@@ -775,7 +800,12 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>https://www.fairfieldresidential.com/property/the-verdant-apartments/</t>
+          <t>https://www.apartments.com/the-verdant-apartments-san-jose-ca/9bng3w5/</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fairfieldresidential.com/apartments/ca/san-jose/the-verdant-apartments/</t>
         </is>
       </c>
     </row>
@@ -884,6 +914,11 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/epic-san-jose-ca/l8r08lg/</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/san-jose/epic</t>
         </is>
       </c>
@@ -993,6 +1028,11 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/elan-at-river-oaks-san-jose-ca/9mqqy17/</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
           <t>https://www.sheaapartments.com/apartments/elan-at-river-oaks/</t>
         </is>
       </c>
@@ -1102,6 +1142,11 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/river-view-apartment-homes-san-jose-ca/3hg41rd/</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
           <t>https://www.irvinecompanyapartments.com/locations/northern-california/san-jose/river-view.html</t>
         </is>
       </c>
@@ -1213,7 +1258,12 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>https://www.apartments.com/vista-99-san-jose-ca/w00sz1l/</t>
+          <t>https://www.apartments.com/vista-99-san-jose-ca/2vres89/</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.equityapartments.com/san-francisco-bay/north-san-jose/vista-99-apartments</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1372,12 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>https://www.greystar.com</t>
+          <t>https://www.apartments.com/passero-santa-clara-ca/vbeyz4d/</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.livepassero.com/</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1488,12 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>https://www.equityapartments.com/san-francisco-bay-area/santa-clara/estancia-at-santa-clara-apartments</t>
+          <t>https://www.apartments.com/estancia-at-santa-clara-santa-clara-ca/bfd2x09/</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.equityapartments.com/san-francisco-bay/santa-clara/estancia-at-santa-clara-apartments</t>
         </is>
       </c>
     </row>
@@ -1544,6 +1604,11 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/river-terrace-santa-clara-ca/dcr4v1l/</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
           <t>https://www.udr.com/san-francisco-bay-area-apartments/santa-clara/river-terrace/</t>
         </is>
       </c>
@@ -1655,7 +1720,12 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>https://www.liveprado.com</t>
+          <t>https://www.apartments.com/prado-santa-clara-ca/b8re69b/</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.liveprado.com/</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1836,12 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>https://www.villasontheboulevard.com</t>
+          <t>https://www.apartments.com/villas-on-the-boulevard-santa-clara-ca/xpzkmpn/</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.villasontheboulevard.com/</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1952,12 @@
       </c>
       <c r="Y16" s="4" t="inlineStr">
         <is>
-          <t>https://www.prometheusapartments.com/santa-clara-ca/mansion-grove/</t>
+          <t>https://www.apartments.com/mansion-grove-santa-clara-ca/l36cb4f/</t>
+        </is>
+      </c>
+      <c r="Z16" s="4" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/ca/santa-clara-apartments/mansion-grove/</t>
         </is>
       </c>
     </row>
@@ -1986,7 +2066,12 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>https://www.antonaspire.com</t>
+          <t>https://www.apartments.com/anton-aspire-milpitas-ca/ptmtmtt/</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.antonaspire.com/</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2180,12 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>https://www.centriaowners.com</t>
+          <t>https://www.apartments.com/centria-milpitas-ca/bvj0p49/</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.centriaowners.com/</t>
         </is>
       </c>
     </row>
@@ -2204,6 +2294,11 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/apex-milpitas-ca/4vnellh/</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/milpitas/apex</t>
         </is>
       </c>
@@ -2315,7 +2410,12 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>https://www.milpitascrossing.com</t>
+          <t>https://www.apartments.com/the-crossing-at-montague-milpitas-ca/843fym2/</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-crossing-at-montague-milpitas-ca/843fym2/</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2526,12 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>https://www.amalfimilpitas.com</t>
+          <t>https://www.apartments.com/amalfi-apartments-milpitas-ca/yy8dzlr/</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>https://amalfimilpitas.com/</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2640,12 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>https://www.livethefields.com/turing</t>
+          <t>https://www.apartments.com/turing-at-the-fields-milpitas-ca/hx52vm1/</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thefieldsmilpitas.com/turing</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2754,12 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>https://sheaproperties.com/apartments/northern-california/sixth-jackson-apartments/</t>
+          <t>https://www.apartments.com/sixth-jackson-san-jose-ca/xkhk1xp/</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sheaapartments.com/apartments/sixth-jackson/</t>
         </is>
       </c>
     </row>
@@ -2753,6 +2868,11 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/the-esplanade-san-jose-ca/fb0vy0r/</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/san-jose/the-esplanade</t>
         </is>
       </c>
@@ -2862,6 +2982,11 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/the-julian-san-jose-ca/few059v/</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
           <t>https://livethejulian.com/</t>
         </is>
       </c>
@@ -2971,7 +3096,12 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>https://www.essexapartmenthomes.com/apartments/san-jose/one-south-market</t>
+          <t>https://www.apartments.com/one-south-market-san-jose-ca/byxczjc/</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>https://onesouthmarket.com/</t>
         </is>
       </c>
     </row>
@@ -3080,6 +3210,11 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/marquis-san-jose-ca/qksmzqz/</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/san-jose/marquis</t>
         </is>
       </c>
@@ -3189,6 +3324,11 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/patina-at-midtown-san-jose-ca/dxd0spl/</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/san-jose/patina-at-midtown</t>
         </is>
       </c>
@@ -3300,6 +3440,11 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/avalon-on-the-alameda-san-jose-ca/pry6zvt/</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
           <t>https://www.avaloncommunities.com/california/san-jose-apartments/avalon-on-the-alameda/</t>
         </is>
       </c>
@@ -3411,7 +3556,12 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>https://www.livelynhaven.com/</t>
+          <t>https://www.apartments.com/lynhaven-san-jose-ca/tb0b949/</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>https://livelynhaven.com/</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3670,12 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>https://www.vespaio.com/</t>
+          <t>https://www.apartments.com/vespaio-san-jose-ca/edr7h7p/</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.millcreekplaces.com/community/vespaio/</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3687,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Viridian Apartments</t>
+          <t>Domain Apartments</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -3609,7 +3764,7 @@
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>Greystar / Institutional (Verified Institutional Community)</t>
+          <t>Greystar / Domain SJ (Verified Institutional Community)</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
@@ -3624,12 +3779,17 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>3233 Zanker Rd, San Jose, CA 95134</t>
+          <t>1 Vista Montana, San Jose, CA 95134</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>https://www.apartments.com/san-jose-ca/</t>
+          <t>https://www.apartments.com/domain-apartments-san-jose-ca/k9lksnc/</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.domainsanjose.com/</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3801,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Cerano Apartments</t>
+          <t>Willow Lake Apartment Homes</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -3718,7 +3878,7 @@
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>Shea Properties (Verified Institutional Developer (Shea))</t>
+          <t>Essex Property Trust (Verified Institutional Developer (Shea))</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
@@ -3733,12 +3893,17 @@
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>575 E Brokaw Rd, San Jose, CA 95112</t>
+          <t>1331 Lakeshore Cir, San Jose, CA 95131</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>https://www.sheaapartments.com/apartments/cerano/</t>
+          <t>https://www.apartments.com/willow-lake-san-jose-ca/1yxldw7/</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.essexapartmenthomes.com/apartments/san-jose/willow-lake</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3915,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Corsa at Market Park (Berryessa BART)</t>
+          <t>Woodland Meadow Apartments</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3827,7 +3992,7 @@
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>Greystar (Verified New-Build Transit Village (2021+))</t>
+          <t>Woodmont Real Estate Services (Verified New-Build Transit Village (2021+))</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -3842,12 +4007,17 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>1550 Berryessa Rd, San Jose, CA 95133</t>
+          <t>1600 Whitewood Dr, San Jose, CA 95131</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>https://www.apartments.com/san-jose-ca/</t>
+          <t>https://www.apartments.com/woodland-meadow-san-jose-ca/v3y9hzd/</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.woodlandmeadow.com/apartments/ca/san-jose/floor-plans</t>
         </is>
       </c>
     </row>
@@ -3956,6 +4126,11 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/santa-clara-square-apartment-homes-santa-clara-ca/rqgtnx3/</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
           <t>https://www.irvinecompanyapartments.com/locations/northern-california/santa-clara/santa-clara-square.html</t>
         </is>
       </c>
@@ -3968,7 +4143,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Riva Terra Apartments</t>
+          <t>Bella Vista Apartments</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -4047,7 +4222,7 @@
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t>Greystar (Verified Institutional Community)</t>
+          <t>Interstate Equities / Bella Vista (Verified Institutional Community)</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
@@ -4062,12 +4237,17 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>2900 Lakeside Dr, Santa Clara, CA 95054</t>
+          <t>1500 Vista Club Cir, Santa Clara, CA 95054</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>https://www.apartments.com/riva-terra-santa-clara-ca/65k9eeu/</t>
+          <t>https://www.apartments.com/bella-vista-santa-clara-ca/lc3w7ng/</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bellavista-apartments.com/</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4259,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Station 1 (Lawrence Station)</t>
+          <t>Marina Cove Apartment Homes</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -4156,7 +4336,7 @@
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>Greystar (Verified Transit-Oriented Community)</t>
+          <t>Essex Property Trust (Verified Transit-Oriented Community)</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
@@ -4171,12 +4351,17 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>3515 Reed Ave, Santa Clara, CA 95051</t>
+          <t>3480 Granada Ave, Santa Clara, CA 95051</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>https://www.apartments.com/santa-clara-ca/</t>
+          <t>https://www.apartments.com/marina-cove-santa-clara-ca/gsl8bkx/</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.essexapartmenthomes.com/apartments/santa-clara/marina-cove</t>
         </is>
       </c>
     </row>
@@ -4285,6 +4470,11 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/avalon-silicon-valley-sunnyvale-ca/we0jcgj/</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
           <t>https://www.avaloncommunities.com/california/sunnyvale-apartments/avalon-silicon-valley/</t>
         </is>
       </c>
@@ -4374,7 +4564,7 @@
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>Prometheus Real Estate Group (Verified Regional Operator (Prometheus))</t>
+          <t>Essex Property Trust (Verified Regional Operator (Prometheus))</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
@@ -4394,7 +4584,12 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>https://prometheusapartments.com/ca/sunnyvale-apartments/solstice/</t>
+          <t>https://www.apartments.com/solstice-sunnyvale-ca/5y4elen/</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.essexapartmenthomes.com/apartments/sunnyvale/solstice</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4698,12 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>https://www.centerrasj.com/</t>
+          <t>https://www.apartments.com/centerra-san-jose-ca/fs8gvdr/</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>https://liveatcenterra.com/</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4812,12 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>https://www.millcreekplaces.com/community/modera-san-pedro-square/</t>
+          <t>https://www.apartments.com/modera-san-pedro-square-san-jose-ca/5m60lvp/</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moderasanpedrosquare.com/</t>
         </is>
       </c>
     </row>
@@ -4721,7 +4926,12 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>https://mirosanjose.com/</t>
+          <t>https://www.apartments.com/miro-san-jose-ca/bsvyvv8/</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rentmiro.com/</t>
         </is>
       </c>
     </row>
@@ -4830,6 +5040,11 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/121-tasman-san-jose-ca/pdbxmnt/</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
           <t>https://www.121tasman.com/</t>
         </is>
       </c>
@@ -4939,6 +5154,11 @@
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/venue-apartments-san-jose-ca/vkhxjjd/</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
           <t>https://www.venue-apts.com/</t>
         </is>
       </c>
@@ -5048,6 +5268,11 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/1036-onofrio-ln-san-jose-ca/zz84sdz/</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
           <t>https://www.theplatformapts.com/</t>
         </is>
       </c>
@@ -5157,7 +5382,12 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>https://www.liveatlinq.com/</t>
+          <t>https://www.apartments.com/linq-san-jose-ca/d325jkj/</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>https://liveatlinq.com/</t>
         </is>
       </c>
     </row>
@@ -5268,6 +5498,11 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/sofi-berryessa-san-jose-ca/pnhhkct/</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
           <t>https://www.sofiberryessa.com/</t>
         </is>
       </c>
@@ -5377,7 +5612,12 @@
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>https://griffisresidential.com/apartments/ca/milpitas/griffis-south-bay/</t>
+          <t>https://www.apartments.com/griffis-south-bay-milpitas-ca/8qvze43/</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>https://griffisresidential.com/property/south-bay/</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5728,12 @@
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>https://www.edgemilpitas.com/</t>
+          <t>https://www.apartments.com/the-edge-milpitas-ca/rn2vmg3/</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>https://edgemilpitas.com/</t>
         </is>
       </c>
     </row>
@@ -5599,6 +5844,11 @@
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/312-gates-dr-milpitas-ca-unit-si-fl2-id2002/r9hml32/</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
           <t>https://www.exploreeleanor.com/</t>
         </is>
       </c>
@@ -5708,6 +5958,11 @@
       </c>
       <c r="Y51" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/the-harlowe-milpitas-ca/ygpz47v/</t>
+        </is>
+      </c>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
           <t>https://www.harloweliving.com/</t>
         </is>
       </c>
@@ -5819,7 +6074,12 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>https://www.lantanamilpitas.com/</t>
+          <t>https://www.apartments.com/lantana-at-milpitas-station-milpitas-ca/2gq4v3c/</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>https://lantanamilpitas.com/</t>
         </is>
       </c>
     </row>
@@ -5928,6 +6188,11 @@
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/ilara-milpitas-ca/cz269te/</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
           <t>https://www.ilaraapartments.com/</t>
         </is>
       </c>
@@ -6039,6 +6304,11 @@
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/mill-creek-milpitas-ca/vm1tzld/</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
           <t>https://www.equityapartments.com/san-francisco-bay/milpitas/mill-creek-apartments</t>
         </is>
       </c>
@@ -6150,7 +6420,12 @@
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>https://www.apartments.com/milpitas-ca/</t>
+          <t>https://www.apartments.com/parc-west-milpitas-ca/sbe86w7/</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.themuirfieldcompany.com/properties</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6536,12 @@
       </c>
       <c r="Y56" s="3" t="inlineStr">
         <is>
-          <t>https://www.sheaapartments.com/</t>
+          <t>https://www.apartments.com/building/terra-serena-luna-milpitas-ca/rws26s0/</t>
+        </is>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/building/terra-serena-luna-milpitas-ca/rws26s0/</t>
         </is>
       </c>
     </row>
@@ -6370,7 +6650,12 @@
       </c>
       <c r="Y57" s="3" t="inlineStr">
         <is>
-          <t>https://www.550moreland.com/</t>
+          <t>https://www.apartments.com/550-moreland-santa-clara-ca/ypyh9ns/</t>
+        </is>
+      </c>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/ca/santa-clara-apartments/550-moreland</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6764,12 @@
       </c>
       <c r="Y58" s="3" t="inlineStr">
         <is>
-          <t>https://www.aveliving.com/locations/san-francisco-bay-area/santa-clara/ave-santa-clara</t>
+          <t>https://www.apartments.com/ave-santa-clara-santa-clara-ca/z3k89nx/</t>
+        </is>
+      </c>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>https://www.aveliving.com/locations/south-bay-silicon-valley/santa-clara</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6878,12 @@
       </c>
       <c r="Y59" s="3" t="inlineStr">
         <is>
-          <t>https://www.thelafayettesantaclara.com/</t>
+          <t>https://www.apartments.com/the-lafayette-santa-clara-ca/c3enymd/</t>
+        </is>
+      </c>
+      <c r="Z59" s="3" t="inlineStr">
+        <is>
+          <t>https://www.livethelafayette.com/</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6992,12 @@
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>https://www.theclaraapartments.com/</t>
+          <t>https://www.apartments.com/the-clara-santa-clara-ca/6b3v70v/</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>https://theclara.com/</t>
         </is>
       </c>
     </row>
@@ -6808,6 +7108,11 @@
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/monticello-apartment-homes-santa-clara-ca/svq6gr4/</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
           <t>https://www.irvinecompanyapartments.com/locations/northern-california/santa-clara/monticello.html</t>
         </is>
       </c>
@@ -6917,6 +7222,11 @@
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/mylo-santa-clara-santa-clara-ca/1rn76d4/</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/santa-clara/mylo-santa-clara</t>
         </is>
       </c>
@@ -7026,6 +7336,11 @@
       </c>
       <c r="Y63" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/lorien-santa-clara-ca/ls5tjef/</t>
+        </is>
+      </c>
+      <c r="Z63" s="3" t="inlineStr">
+        <is>
           <t>https://www.equityapartments.com/san-francisco-bay/santa-clara/lorien-apartments</t>
         </is>
       </c>
@@ -7137,7 +7452,12 @@
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>https://www.deanzaproperties.com/apartments/ca/santa-clara/catalina-luxury-apartments/</t>
+          <t>https://www.apartments.com/catalina-luxury-apartments-santa-clara-ca/5d8x1hm/</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deanzaproperties.com/south-bay-area/catalina-luxury-apartments/</t>
         </is>
       </c>
     </row>
@@ -7248,6 +7568,11 @@
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/villa-granada-santa-clara-ca/q89dqzw/</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/santa-clara/villa-granada</t>
         </is>
       </c>
@@ -7357,7 +7682,12 @@
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>https://www.prometheusapartments.com/ca/santa-clara-apartments/cobalt</t>
+          <t>https://www.apartments.com/cobalt-santa-clara-ca/pnpkzps/</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/ca/santa-clara-apartments/cobalt</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7796,12 @@
       </c>
       <c r="Y67" s="3" t="inlineStr">
         <is>
-          <t>https://www.hollandresidential.com/ca/santa-clara/orlo</t>
+          <t>https://www.apartments.com/orlo-and-alba-santa-clara-ca/1pw4vv6/</t>
+        </is>
+      </c>
+      <c r="Z67" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hollandresidential.com/ca/santa-clara/orlo-alba</t>
         </is>
       </c>
     </row>
@@ -7575,6 +7910,11 @@
       </c>
       <c r="Y68" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/domicilio-santa-clara-ca/6x81pwt/</t>
+        </is>
+      </c>
+      <c r="Z68" s="3" t="inlineStr">
+        <is>
           <t>https://www.domicilioapts.com/</t>
         </is>
       </c>
@@ -7684,7 +8024,12 @@
       </c>
       <c r="Y69" s="3" t="inlineStr">
         <is>
-          <t>https://www.missionpointebywindsor.com/</t>
+          <t>https://www.apartments.com/mission-pointe-by-windsor-sunnyvale-ca/j83gb95/</t>
+        </is>
+      </c>
+      <c r="Z69" s="3" t="inlineStr">
+        <is>
+          <t>https://www.windsorcommunities.com/properties/mission-pointe-by-windsor/</t>
         </is>
       </c>
     </row>
@@ -7793,6 +8138,11 @@
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/encasa-sunnyvale-ca/s1ktnb6/</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
           <t>https://www.encasaliving.com/</t>
         </is>
       </c>
@@ -7904,6 +8254,11 @@
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/the-arches-sunnyvale-ca/fvycn0r/</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
           <t>https://www.equityapartments.com/san-francisco-bay/sunnyvale/the-arches-apartments</t>
         </is>
       </c>
@@ -8013,6 +8368,11 @@
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/the-montclaire-sunnyvale-ca/x4m85qp/</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/sunnyvale/the-montclaire</t>
         </is>
       </c>
@@ -8124,6 +8484,11 @@
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/windsor-ridge-sunnyvale-ca/nsgs57p/</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/sunnyvale/windsor-ridge</t>
         </is>
       </c>
@@ -8235,6 +8600,11 @@
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/briarwood-sunnyvale-ca/v07q4kg/</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
           <t>https://www.equityapartments.com/san-francisco-bay/sunnyvale/briarwood-apartments</t>
         </is>
       </c>
@@ -8344,7 +8714,12 @@
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>https://prometheusapartments.com/ca/sunnyvale-apartments/spruce/</t>
+          <t>https://www.apartments.com/spruce-apartments-sunnyvale-ca/prxrltv/</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/ca/sunnyvale-apartments/spruce</t>
         </is>
       </c>
     </row>
@@ -8453,6 +8828,11 @@
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/arbor-terrace-sunnyvale-ca/z3qzypx/</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
           <t>https://www.equityapartments.com/san-francisco-bay/sunnyvale/arbor-terrace-apartments</t>
         </is>
       </c>
@@ -8564,6 +8944,11 @@
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/magnolia-square-sunnyvale-ca/zstdbqz/</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/sunnyvale/magnolia-square</t>
         </is>
       </c>
@@ -8675,7 +9060,12 @@
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>https://www.windsorcommunities.com/properties/pavona/</t>
+          <t>https://www.apartments.com/pavona-apartments-san-jose-ca/qf6de5z/</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.windsorcommunities.com/properties/pavona-apartments/</t>
         </is>
       </c>
     </row>
@@ -8784,6 +9174,11 @@
       </c>
       <c r="Y79" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/cannery-park-by-windsor-san-jose-ca/43ekybk/</t>
+        </is>
+      </c>
+      <c r="Z79" s="3" t="inlineStr">
+        <is>
           <t>https://www.windsorcommunities.com/properties/cannery-park-by-windsor/</t>
         </is>
       </c>
@@ -8893,7 +9288,12 @@
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>https://www.apartments.com/villa-torino-san-jose-ca/</t>
+          <t>https://www.apartments.com/villa-torino-san-jose-ca/40372th/</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.villatorinoapts.com/</t>
         </is>
       </c>
     </row>
@@ -9002,6 +9402,11 @@
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/360-residences-san-jose-ca/xx7h13n/</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/san-jose/360-residences</t>
         </is>
       </c>
@@ -9014,7 +9419,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>The Fay (SoFA Luxury Tower)</t>
+          <t>Flow San Jose (formerly The Fay)</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -9111,7 +9516,12 @@
       </c>
       <c r="Y82" s="3" t="inlineStr">
         <is>
-          <t>https://www.thefaysj.com/</t>
+          <t>https://www.apartments.com/flow-san-jose-san-jose-ca/12knvq5/</t>
+        </is>
+      </c>
+      <c r="Z82" s="3" t="inlineStr">
+        <is>
+          <t>https://flow.life/en/properties/san-jose</t>
         </is>
       </c>
     </row>
@@ -9220,6 +9630,11 @@
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/the-pierce-san-jose-ca/533ct9n/</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
           <t>https://www.thepierce.com/</t>
         </is>
       </c>
@@ -9324,12 +9739,17 @@
       </c>
       <c r="X84" s="3" t="inlineStr">
         <is>
-          <t>715 W Julian St, San Jose, CA 95126</t>
+          <t>717 W Julian St, San Jose, CA 95126</t>
         </is>
       </c>
       <c r="Y84" s="3" t="inlineStr">
         <is>
-          <t>https://www.diridonwest.com/</t>
+          <t>https://www.apartments.com/diridon-west-san-jose-ca/l194cvd/</t>
+        </is>
+      </c>
+      <c r="Z84" s="3" t="inlineStr">
+        <is>
+          <t>https://diridonwest.com/</t>
         </is>
       </c>
     </row>
@@ -9341,7 +9761,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Modera The Alameda</t>
+          <t>787 The Alameda (formerly Modera The Alameda)</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -9438,7 +9858,12 @@
       </c>
       <c r="Y85" s="3" t="inlineStr">
         <is>
-          <t>https://www.millcreekplaces.com/community/modera-the-alameda/</t>
+          <t>https://www.apartments.com/787-the-alameda-san-jose-ca/7f64s5w/</t>
+        </is>
+      </c>
+      <c r="Z85" s="3" t="inlineStr">
+        <is>
+          <t>https://www.787thealameda.com/</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9875,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Avalon Morrison Park</t>
+          <t>Bell Diridon (formerly Avalon Morrison Park)</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -9549,7 +9974,12 @@
       </c>
       <c r="Y86" s="3" t="inlineStr">
         <is>
-          <t>https://www.avaloncommunities.com/california/san-jose-apartments/avalon-morrison-park/</t>
+          <t>https://www.apartments.com/bell-diridon-san-jose-ca/q9197cx/</t>
+        </is>
+      </c>
+      <c r="Z86" s="3" t="inlineStr">
+        <is>
+          <t>https://www.belldiridon.com/</t>
         </is>
       </c>
     </row>
@@ -9658,7 +10088,12 @@
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>https://www.meridianmidtown.com/</t>
+          <t>https://www.apartments.com/meridian-at-midtown-san-jose-ca/ezyhf1m/</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>https://meridianmidtown.com/</t>
         </is>
       </c>
     </row>
@@ -9769,7 +10204,12 @@
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>https://www.elementsmidtown.com/</t>
+          <t>https://www.apartments.com/elements-san-jose-ca/v3ky8zd/</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.elementsapts.com/</t>
         </is>
       </c>
     </row>
@@ -9878,6 +10318,11 @@
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/808-west-apartments-san-jose-ca/402fkjh/</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
           <t>https://www.808west-apts.com/</t>
         </is>
       </c>
@@ -9989,6 +10434,11 @@
       </c>
       <c r="Y90" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/embark-apartments-fremont-ca/c2hfn5g/</t>
+        </is>
+      </c>
+      <c r="Z90" s="3" t="inlineStr">
+        <is>
           <t>https://www.embarkapartments.com/</t>
         </is>
       </c>
@@ -10001,7 +10451,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Amara at Tasman East</t>
+          <t>Marina Playa Apartment Homes</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -10078,7 +10528,7 @@
       </c>
       <c r="U91" s="3" t="inlineStr">
         <is>
-          <t>Greystar (Verified Active Community (Greystar))</t>
+          <t>UDR (Verified Active Community (Greystar))</t>
         </is>
       </c>
       <c r="V91" s="3" t="inlineStr">
@@ -10093,12 +10543,17 @@
       </c>
       <c r="X91" s="3" t="inlineStr">
         <is>
-          <t>2233 Calle Del Mundo, Santa Clara, CA 95054</t>
+          <t>3500 Granada Ave, Santa Clara, CA 95051</t>
         </is>
       </c>
       <c r="Y91" s="3" t="inlineStr">
         <is>
-          <t>https://www.greystar.com/</t>
+          <t>https://www.apartments.com/marina-playa-santa-clara-ca/d6tg4dk/</t>
+        </is>
+      </c>
+      <c r="Z91" s="3" t="inlineStr">
+        <is>
+          <t>https://www.udr.com/san-francisco-bay-area-apartments/santa-clara/marina-playa/</t>
         </is>
       </c>
     </row>
@@ -10204,12 +10659,17 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>2250 Monroe St, Santa Clara, CA 95050</t>
+          <t>4500 Carlyle Ct, Santa Clara, CA 95054</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>https://www.apartments.com/the-carlyle-santa-clara-ca/</t>
+          <t>https://www.apartments.com/carlyle-santa-clara-ca/j7b5mj7/</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thecarlyle-apartments.com/</t>
         </is>
       </c>
     </row>
@@ -10227,7 +10687,7 @@
     <col min="17" max="20" width="13" customWidth="1"/>
     <col min="21" max="21" width="28" customWidth="1"/>
     <col min="22" max="23" width="46" customWidth="1"/>
-    <col min="24" max="25" width="36" customWidth="1"/>
+    <col min="24" max="26" width="38" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -10353,6 +10813,11 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>Apartments.com Listing</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>Official Website</t>
         </is>
       </c>
@@ -10462,6 +10927,11 @@
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/north-park-apartment-homes-san-jose-ca/fsbvjbs/</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
           <t>https://www.irvinecompanyapartments.com/locations/northern-california/san-jose/north-park.html</t>
         </is>
       </c>
@@ -10571,6 +11041,11 @@
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/crescent-village-apartment-homes-san-jose-ca/kb57kc8/</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
           <t>https://www.irvinecompanyapartments.com/locations/northern-california/san-jose/crescent-village.html</t>
         </is>
       </c>
@@ -10680,6 +11155,11 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/enso-san-jose-ca/e5b3e4m/</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/san-jose/enso</t>
         </is>
       </c>
@@ -10789,7 +11269,12 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>https://www.aireliving.com/</t>
+          <t>https://www.apartments.com/aire-san-jose-ca/nrsnnzq/</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>https://aireliving.com/</t>
         </is>
       </c>
     </row>
@@ -10898,7 +11383,12 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>https://www.greystar.com</t>
+          <t>https://www.apartments.com/passero-santa-clara-ca/vbeyz4d/</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.livepassero.com/</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11499,12 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>https://www.equityapartments.com/san-francisco-bay-area/santa-clara/estancia-at-santa-clara-apartments</t>
+          <t>https://www.apartments.com/estancia-at-santa-clara-santa-clara-ca/bfd2x09/</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.equityapartments.com/san-francisco-bay/santa-clara/estancia-at-santa-clara-apartments</t>
         </is>
       </c>
     </row>
@@ -11118,7 +11613,12 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>https://www.antonaspire.com</t>
+          <t>https://www.apartments.com/anton-aspire-milpitas-ca/ptmtmtt/</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.antonaspire.com/</t>
         </is>
       </c>
     </row>
@@ -11227,7 +11727,12 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>https://www.centriaowners.com</t>
+          <t>https://www.apartments.com/centria-milpitas-ca/bvj0p49/</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.centriaowners.com/</t>
         </is>
       </c>
     </row>
@@ -11336,6 +11841,11 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/apex-milpitas-ca/4vnellh/</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/milpitas/apex</t>
         </is>
       </c>
@@ -11447,7 +11957,12 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>https://www.milpitascrossing.com</t>
+          <t>https://www.apartments.com/the-crossing-at-montague-milpitas-ca/843fym2/</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-crossing-at-montague-milpitas-ca/843fym2/</t>
         </is>
       </c>
     </row>
@@ -11558,7 +12073,12 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>https://www.amalfimilpitas.com</t>
+          <t>https://www.apartments.com/amalfi-apartments-milpitas-ca/yy8dzlr/</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>https://amalfimilpitas.com/</t>
         </is>
       </c>
     </row>
@@ -11667,7 +12187,12 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>https://www.livethefields.com/turing</t>
+          <t>https://www.apartments.com/turing-at-the-fields-milpitas-ca/hx52vm1/</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thefieldsmilpitas.com/turing</t>
         </is>
       </c>
     </row>
@@ -11776,7 +12301,12 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>https://sheaproperties.com/apartments/northern-california/sixth-jackson-apartments/</t>
+          <t>https://www.apartments.com/sixth-jackson-san-jose-ca/xkhk1xp/</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sheaapartments.com/apartments/sixth-jackson/</t>
         </is>
       </c>
     </row>
@@ -11885,6 +12415,11 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/the-esplanade-san-jose-ca/fb0vy0r/</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/san-jose/the-esplanade</t>
         </is>
       </c>
@@ -11994,6 +12529,11 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/the-julian-san-jose-ca/few059v/</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
           <t>https://livethejulian.com/</t>
         </is>
       </c>
@@ -12103,7 +12643,12 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>https://www.essexapartmenthomes.com/apartments/san-jose/one-south-market</t>
+          <t>https://www.apartments.com/one-south-market-san-jose-ca/byxczjc/</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>https://onesouthmarket.com/</t>
         </is>
       </c>
     </row>
@@ -12212,6 +12757,11 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/marquis-san-jose-ca/qksmzqz/</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/san-jose/marquis</t>
         </is>
       </c>
@@ -12321,6 +12871,11 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/patina-at-midtown-san-jose-ca/dxd0spl/</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/san-jose/patina-at-midtown</t>
         </is>
       </c>
@@ -12432,6 +12987,11 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/avalon-on-the-alameda-san-jose-ca/pry6zvt/</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
           <t>https://www.avaloncommunities.com/california/san-jose-apartments/avalon-on-the-alameda/</t>
         </is>
       </c>
@@ -12541,7 +13101,12 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>https://www.vespaio.com/</t>
+          <t>https://www.apartments.com/vespaio-san-jose-ca/edr7h7p/</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.millcreekplaces.com/community/vespaio/</t>
         </is>
       </c>
     </row>
@@ -12553,7 +13118,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Viridian Apartments</t>
+          <t>Domain Apartments</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -12630,7 +13195,7 @@
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>Greystar / Institutional (Verified Institutional Community)</t>
+          <t>Greystar / Domain SJ (Verified Institutional Community)</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
@@ -12645,12 +13210,17 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>3233 Zanker Rd, San Jose, CA 95134</t>
+          <t>1 Vista Montana, San Jose, CA 95134</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>https://www.apartments.com/san-jose-ca/</t>
+          <t>https://www.apartments.com/domain-apartments-san-jose-ca/k9lksnc/</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.domainsanjose.com/</t>
         </is>
       </c>
     </row>
@@ -12662,7 +13232,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Cerano Apartments</t>
+          <t>Willow Lake Apartment Homes</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -12739,7 +13309,7 @@
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>Shea Properties (Verified Institutional Developer (Shea))</t>
+          <t>Essex Property Trust (Verified Institutional Developer (Shea))</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
@@ -12754,12 +13324,17 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>575 E Brokaw Rd, San Jose, CA 95112</t>
+          <t>1331 Lakeshore Cir, San Jose, CA 95131</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>https://www.sheaapartments.com/apartments/cerano/</t>
+          <t>https://www.apartments.com/willow-lake-san-jose-ca/1yxldw7/</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.essexapartmenthomes.com/apartments/san-jose/willow-lake</t>
         </is>
       </c>
     </row>
@@ -12771,7 +13346,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Corsa at Market Park (Berryessa BART)</t>
+          <t>Woodland Meadow Apartments</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -12848,7 +13423,7 @@
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>Greystar (Verified New-Build Transit Village (2021+))</t>
+          <t>Woodmont Real Estate Services (Verified New-Build Transit Village (2021+))</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -12863,12 +13438,17 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>1550 Berryessa Rd, San Jose, CA 95133</t>
+          <t>1600 Whitewood Dr, San Jose, CA 95131</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>https://www.apartments.com/san-jose-ca/</t>
+          <t>https://www.apartments.com/woodland-meadow-san-jose-ca/v3y9hzd/</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.woodlandmeadow.com/apartments/ca/san-jose/floor-plans</t>
         </is>
       </c>
     </row>
@@ -12977,6 +13557,11 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/santa-clara-square-apartment-homes-santa-clara-ca/rqgtnx3/</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
           <t>https://www.irvinecompanyapartments.com/locations/northern-california/santa-clara/santa-clara-square.html</t>
         </is>
       </c>
@@ -12989,7 +13574,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Riva Terra Apartments</t>
+          <t>Bella Vista Apartments</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -13068,7 +13653,7 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>Greystar (Verified Institutional Community)</t>
+          <t>Interstate Equities / Bella Vista (Verified Institutional Community)</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
@@ -13083,12 +13668,17 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>2900 Lakeside Dr, Santa Clara, CA 95054</t>
+          <t>1500 Vista Club Cir, Santa Clara, CA 95054</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>https://www.apartments.com/riva-terra-santa-clara-ca/65k9eeu/</t>
+          <t>https://www.apartments.com/bella-vista-santa-clara-ca/lc3w7ng/</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bellavista-apartments.com/</t>
         </is>
       </c>
     </row>
@@ -13100,7 +13690,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Station 1 (Lawrence Station)</t>
+          <t>Marina Cove Apartment Homes</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -13177,7 +13767,7 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t>Greystar (Verified Transit-Oriented Community)</t>
+          <t>Essex Property Trust (Verified Transit-Oriented Community)</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
@@ -13192,12 +13782,17 @@
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>3515 Reed Ave, Santa Clara, CA 95051</t>
+          <t>3480 Granada Ave, Santa Clara, CA 95051</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>https://www.apartments.com/santa-clara-ca/</t>
+          <t>https://www.apartments.com/marina-cove-santa-clara-ca/gsl8bkx/</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.essexapartmenthomes.com/apartments/santa-clara/marina-cove</t>
         </is>
       </c>
     </row>
@@ -13306,6 +13901,11 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/avalon-silicon-valley-sunnyvale-ca/we0jcgj/</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
           <t>https://www.avaloncommunities.com/california/sunnyvale-apartments/avalon-silicon-valley/</t>
         </is>
       </c>
@@ -13395,7 +13995,7 @@
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>Prometheus Real Estate Group (Verified Regional Operator (Prometheus))</t>
+          <t>Essex Property Trust (Verified Regional Operator (Prometheus))</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -13415,7 +14015,12 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>https://prometheusapartments.com/ca/sunnyvale-apartments/solstice/</t>
+          <t>https://www.apartments.com/solstice-sunnyvale-ca/5y4elen/</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.essexapartmenthomes.com/apartments/sunnyvale/solstice</t>
         </is>
       </c>
     </row>
@@ -13524,7 +14129,12 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>https://www.centerrasj.com/</t>
+          <t>https://www.apartments.com/centerra-san-jose-ca/fs8gvdr/</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>https://liveatcenterra.com/</t>
         </is>
       </c>
     </row>
@@ -13633,7 +14243,12 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>https://www.millcreekplaces.com/community/modera-san-pedro-square/</t>
+          <t>https://www.apartments.com/modera-san-pedro-square-san-jose-ca/5m60lvp/</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moderasanpedrosquare.com/</t>
         </is>
       </c>
     </row>
@@ -13742,7 +14357,12 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>https://mirosanjose.com/</t>
+          <t>https://www.apartments.com/miro-san-jose-ca/bsvyvv8/</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rentmiro.com/</t>
         </is>
       </c>
     </row>
@@ -13851,6 +14471,11 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/venue-apartments-san-jose-ca/vkhxjjd/</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
           <t>https://www.venue-apts.com/</t>
         </is>
       </c>
@@ -13960,7 +14585,12 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>https://www.liveatlinq.com/</t>
+          <t>https://www.apartments.com/linq-san-jose-ca/d325jkj/</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>https://liveatlinq.com/</t>
         </is>
       </c>
     </row>
@@ -14069,7 +14699,12 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>https://griffisresidential.com/apartments/ca/milpitas/griffis-south-bay/</t>
+          <t>https://www.apartments.com/griffis-south-bay-milpitas-ca/8qvze43/</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>https://griffisresidential.com/property/south-bay/</t>
         </is>
       </c>
     </row>
@@ -14178,6 +14813,11 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/the-harlowe-milpitas-ca/ygpz47v/</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
           <t>https://www.harloweliving.com/</t>
         </is>
       </c>
@@ -14287,6 +14927,11 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/ilara-milpitas-ca/cz269te/</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
           <t>https://www.ilaraapartments.com/</t>
         </is>
       </c>
@@ -14398,6 +15043,11 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/mill-creek-milpitas-ca/vm1tzld/</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
           <t>https://www.equityapartments.com/san-francisco-bay/milpitas/mill-creek-apartments</t>
         </is>
       </c>
@@ -14509,7 +15159,12 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>https://www.apartments.com/milpitas-ca/</t>
+          <t>https://www.apartments.com/parc-west-milpitas-ca/sbe86w7/</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.themuirfieldcompany.com/properties</t>
         </is>
       </c>
     </row>
@@ -14620,7 +15275,12 @@
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>https://www.sheaapartments.com/</t>
+          <t>https://www.apartments.com/building/terra-serena-luna-milpitas-ca/rws26s0/</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/building/terra-serena-luna-milpitas-ca/rws26s0/</t>
         </is>
       </c>
     </row>
@@ -14729,7 +15389,12 @@
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>https://www.550moreland.com/</t>
+          <t>https://www.apartments.com/550-moreland-santa-clara-ca/ypyh9ns/</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/ca/santa-clara-apartments/550-moreland</t>
         </is>
       </c>
     </row>
@@ -14838,7 +15503,12 @@
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>https://www.aveliving.com/locations/san-francisco-bay-area/santa-clara/ave-santa-clara</t>
+          <t>https://www.apartments.com/ave-santa-clara-santa-clara-ca/z3k89nx/</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>https://www.aveliving.com/locations/south-bay-silicon-valley/santa-clara</t>
         </is>
       </c>
     </row>
@@ -14947,7 +15617,12 @@
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>https://www.thelafayettesantaclara.com/</t>
+          <t>https://www.apartments.com/the-lafayette-santa-clara-ca/c3enymd/</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.livethelafayette.com/</t>
         </is>
       </c>
     </row>
@@ -15056,6 +15731,11 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/mylo-santa-clara-santa-clara-ca/1rn76d4/</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/santa-clara/mylo-santa-clara</t>
         </is>
       </c>
@@ -15165,6 +15845,11 @@
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/lorien-santa-clara-ca/ls5tjef/</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
           <t>https://www.equityapartments.com/san-francisco-bay/santa-clara/lorien-apartments</t>
         </is>
       </c>
@@ -15274,7 +15959,12 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>https://www.hollandresidential.com/ca/santa-clara/orlo</t>
+          <t>https://www.apartments.com/orlo-and-alba-santa-clara-ca/1pw4vv6/</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hollandresidential.com/ca/santa-clara/orlo-alba</t>
         </is>
       </c>
     </row>
@@ -15383,6 +16073,11 @@
       </c>
       <c r="Y47" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/domicilio-santa-clara-ca/6x81pwt/</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
           <t>https://www.domicilioapts.com/</t>
         </is>
       </c>
@@ -15492,7 +16187,12 @@
       </c>
       <c r="Y48" s="3" t="inlineStr">
         <is>
-          <t>https://www.missionpointebywindsor.com/</t>
+          <t>https://www.apartments.com/mission-pointe-by-windsor-sunnyvale-ca/j83gb95/</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>https://www.windsorcommunities.com/properties/mission-pointe-by-windsor/</t>
         </is>
       </c>
     </row>
@@ -15601,6 +16301,11 @@
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/the-montclaire-sunnyvale-ca/x4m85qp/</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/sunnyvale/the-montclaire</t>
         </is>
       </c>
@@ -15710,7 +16415,12 @@
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>https://prometheusapartments.com/ca/sunnyvale-apartments/spruce/</t>
+          <t>https://www.apartments.com/spruce-apartments-sunnyvale-ca/prxrltv/</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/ca/sunnyvale-apartments/spruce</t>
         </is>
       </c>
     </row>
@@ -15819,6 +16529,11 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/arbor-terrace-sunnyvale-ca/z3qzypx/</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
           <t>https://www.equityapartments.com/san-francisco-bay/sunnyvale/arbor-terrace-apartments</t>
         </is>
       </c>
@@ -15928,6 +16643,11 @@
       </c>
       <c r="Y52" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/cannery-park-by-windsor-san-jose-ca/43ekybk/</t>
+        </is>
+      </c>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
           <t>https://www.windsorcommunities.com/properties/cannery-park-by-windsor/</t>
         </is>
       </c>
@@ -16037,7 +16757,12 @@
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>https://www.apartments.com/villa-torino-san-jose-ca/</t>
+          <t>https://www.apartments.com/villa-torino-san-jose-ca/40372th/</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.villatorinoapts.com/</t>
         </is>
       </c>
     </row>
@@ -16146,6 +16871,11 @@
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/360-residences-san-jose-ca/xx7h13n/</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/san-jose/360-residences</t>
         </is>
       </c>
@@ -16158,7 +16888,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>The Fay (SoFA Luxury Tower)</t>
+          <t>Flow San Jose (formerly The Fay)</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -16255,7 +16985,12 @@
       </c>
       <c r="Y55" s="3" t="inlineStr">
         <is>
-          <t>https://www.thefaysj.com/</t>
+          <t>https://www.apartments.com/flow-san-jose-san-jose-ca/12knvq5/</t>
+        </is>
+      </c>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>https://flow.life/en/properties/san-jose</t>
         </is>
       </c>
     </row>
@@ -16359,12 +17094,17 @@
       </c>
       <c r="X56" s="3" t="inlineStr">
         <is>
-          <t>715 W Julian St, San Jose, CA 95126</t>
+          <t>717 W Julian St, San Jose, CA 95126</t>
         </is>
       </c>
       <c r="Y56" s="3" t="inlineStr">
         <is>
-          <t>https://www.diridonwest.com/</t>
+          <t>https://www.apartments.com/diridon-west-san-jose-ca/l194cvd/</t>
+        </is>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>https://diridonwest.com/</t>
         </is>
       </c>
     </row>
@@ -16376,7 +17116,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Modera The Alameda</t>
+          <t>787 The Alameda (formerly Modera The Alameda)</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -16473,7 +17213,12 @@
       </c>
       <c r="Y57" s="3" t="inlineStr">
         <is>
-          <t>https://www.millcreekplaces.com/community/modera-the-alameda/</t>
+          <t>https://www.apartments.com/787-the-alameda-san-jose-ca/7f64s5w/</t>
+        </is>
+      </c>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>https://www.787thealameda.com/</t>
         </is>
       </c>
     </row>
@@ -16485,7 +17230,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Avalon Morrison Park</t>
+          <t>Bell Diridon (formerly Avalon Morrison Park)</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -16584,7 +17329,12 @@
       </c>
       <c r="Y58" s="3" t="inlineStr">
         <is>
-          <t>https://www.avaloncommunities.com/california/san-jose-apartments/avalon-morrison-park/</t>
+          <t>https://www.apartments.com/bell-diridon-san-jose-ca/q9197cx/</t>
+        </is>
+      </c>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>https://www.belldiridon.com/</t>
         </is>
       </c>
     </row>
@@ -16693,7 +17443,12 @@
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>https://www.meridianmidtown.com/</t>
+          <t>https://www.apartments.com/meridian-at-midtown-san-jose-ca/ezyhf1m/</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>https://meridianmidtown.com/</t>
         </is>
       </c>
     </row>
@@ -16804,6 +17559,11 @@
       </c>
       <c r="Y60" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/embark-apartments-fremont-ca/c2hfn5g/</t>
+        </is>
+      </c>
+      <c r="Z60" s="3" t="inlineStr">
+        <is>
           <t>https://www.embarkapartments.com/</t>
         </is>
       </c>
@@ -16816,7 +17576,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Amara at Tasman East</t>
+          <t>Marina Playa Apartment Homes</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -16893,7 +17653,7 @@
       </c>
       <c r="U61" s="3" t="inlineStr">
         <is>
-          <t>Greystar (Verified Active Community (Greystar))</t>
+          <t>UDR (Verified Active Community (Greystar))</t>
         </is>
       </c>
       <c r="V61" s="3" t="inlineStr">
@@ -16908,12 +17668,17 @@
       </c>
       <c r="X61" s="3" t="inlineStr">
         <is>
-          <t>2233 Calle Del Mundo, Santa Clara, CA 95054</t>
+          <t>3500 Granada Ave, Santa Clara, CA 95051</t>
         </is>
       </c>
       <c r="Y61" s="3" t="inlineStr">
         <is>
-          <t>https://www.greystar.com/</t>
+          <t>https://www.apartments.com/marina-playa-santa-clara-ca/d6tg4dk/</t>
+        </is>
+      </c>
+      <c r="Z61" s="3" t="inlineStr">
+        <is>
+          <t>https://www.udr.com/san-francisco-bay-area-apartments/santa-clara/marina-playa/</t>
         </is>
       </c>
     </row>
@@ -17019,12 +17784,17 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>2250 Monroe St, Santa Clara, CA 95050</t>
+          <t>4500 Carlyle Ct, Santa Clara, CA 95054</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>https://www.apartments.com/the-carlyle-santa-clara-ca/</t>
+          <t>https://www.apartments.com/carlyle-santa-clara-ca/j7b5mj7/</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thecarlyle-apartments.com/</t>
         </is>
       </c>
     </row>
@@ -17042,7 +17812,7 @@
     <col min="17" max="20" width="13" customWidth="1"/>
     <col min="21" max="21" width="28" customWidth="1"/>
     <col min="22" max="23" width="46" customWidth="1"/>
-    <col min="24" max="25" width="36" customWidth="1"/>
+    <col min="24" max="26" width="38" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -17168,6 +17938,11 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>Apartments.com Listing</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>Official Website</t>
         </is>
       </c>
@@ -17277,7 +18052,12 @@
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>https://www.greystar.com</t>
+          <t>https://www.apartments.com/passero-santa-clara-ca/vbeyz4d/</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.livepassero.com/</t>
         </is>
       </c>
     </row>
@@ -17388,7 +18168,12 @@
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>https://www.equityapartments.com/san-francisco-bay-area/santa-clara/estancia-at-santa-clara-apartments</t>
+          <t>https://www.apartments.com/estancia-at-santa-clara-santa-clara-ca/bfd2x09/</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.equityapartments.com/san-francisco-bay/santa-clara/estancia-at-santa-clara-apartments</t>
         </is>
       </c>
     </row>
@@ -17499,6 +18284,11 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/river-terrace-santa-clara-ca/dcr4v1l/</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
           <t>https://www.udr.com/san-francisco-bay-area-apartments/santa-clara/river-terrace/</t>
         </is>
       </c>
@@ -17610,7 +18400,12 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>https://www.liveprado.com</t>
+          <t>https://www.apartments.com/prado-santa-clara-ca/b8re69b/</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.liveprado.com/</t>
         </is>
       </c>
     </row>
@@ -17721,7 +18516,12 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>https://www.villasontheboulevard.com</t>
+          <t>https://www.apartments.com/villas-on-the-boulevard-santa-clara-ca/xpzkmpn/</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.villasontheboulevard.com/</t>
         </is>
       </c>
     </row>
@@ -17832,7 +18632,12 @@
       </c>
       <c r="Y7" s="4" t="inlineStr">
         <is>
-          <t>https://www.prometheusapartments.com/santa-clara-ca/mansion-grove/</t>
+          <t>https://www.apartments.com/mansion-grove-santa-clara-ca/l36cb4f/</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/ca/santa-clara-apartments/mansion-grove/</t>
         </is>
       </c>
     </row>
@@ -17941,6 +18746,11 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/santa-clara-square-apartment-homes-santa-clara-ca/rqgtnx3/</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
           <t>https://www.irvinecompanyapartments.com/locations/northern-california/santa-clara/santa-clara-square.html</t>
         </is>
       </c>
@@ -17953,7 +18763,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Riva Terra Apartments</t>
+          <t>Bella Vista Apartments</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -18032,7 +18842,7 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>Greystar (Verified Institutional Community)</t>
+          <t>Interstate Equities / Bella Vista (Verified Institutional Community)</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
@@ -18047,12 +18857,17 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>2900 Lakeside Dr, Santa Clara, CA 95054</t>
+          <t>1500 Vista Club Cir, Santa Clara, CA 95054</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>https://www.apartments.com/riva-terra-santa-clara-ca/65k9eeu/</t>
+          <t>https://www.apartments.com/bella-vista-santa-clara-ca/lc3w7ng/</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bellavista-apartments.com/</t>
         </is>
       </c>
     </row>
@@ -18064,7 +18879,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Station 1 (Lawrence Station)</t>
+          <t>Marina Cove Apartment Homes</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -18141,7 +18956,7 @@
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>Greystar (Verified Transit-Oriented Community)</t>
+          <t>Essex Property Trust (Verified Transit-Oriented Community)</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
@@ -18156,12 +18971,17 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>3515 Reed Ave, Santa Clara, CA 95051</t>
+          <t>3480 Granada Ave, Santa Clara, CA 95051</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>https://www.apartments.com/santa-clara-ca/</t>
+          <t>https://www.apartments.com/marina-cove-santa-clara-ca/gsl8bkx/</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.essexapartmenthomes.com/apartments/santa-clara/marina-cove</t>
         </is>
       </c>
     </row>
@@ -18270,7 +19090,12 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>https://www.550moreland.com/</t>
+          <t>https://www.apartments.com/550-moreland-santa-clara-ca/ypyh9ns/</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/ca/santa-clara-apartments/550-moreland</t>
         </is>
       </c>
     </row>
@@ -18379,7 +19204,12 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>https://www.aveliving.com/locations/san-francisco-bay-area/santa-clara/ave-santa-clara</t>
+          <t>https://www.apartments.com/ave-santa-clara-santa-clara-ca/z3k89nx/</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.aveliving.com/locations/south-bay-silicon-valley/santa-clara</t>
         </is>
       </c>
     </row>
@@ -18488,7 +19318,12 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>https://www.thelafayettesantaclara.com/</t>
+          <t>https://www.apartments.com/the-lafayette-santa-clara-ca/c3enymd/</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.livethelafayette.com/</t>
         </is>
       </c>
     </row>
@@ -18597,7 +19432,12 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>https://www.theclaraapartments.com/</t>
+          <t>https://www.apartments.com/the-clara-santa-clara-ca/6b3v70v/</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>https://theclara.com/</t>
         </is>
       </c>
     </row>
@@ -18708,6 +19548,11 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/monticello-apartment-homes-santa-clara-ca/svq6gr4/</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
           <t>https://www.irvinecompanyapartments.com/locations/northern-california/santa-clara/monticello.html</t>
         </is>
       </c>
@@ -18817,6 +19662,11 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/mylo-santa-clara-santa-clara-ca/1rn76d4/</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/santa-clara/mylo-santa-clara</t>
         </is>
       </c>
@@ -18926,6 +19776,11 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/lorien-santa-clara-ca/ls5tjef/</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
           <t>https://www.equityapartments.com/san-francisco-bay/santa-clara/lorien-apartments</t>
         </is>
       </c>
@@ -19037,7 +19892,12 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>https://www.deanzaproperties.com/apartments/ca/santa-clara/catalina-luxury-apartments/</t>
+          <t>https://www.apartments.com/catalina-luxury-apartments-santa-clara-ca/5d8x1hm/</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deanzaproperties.com/south-bay-area/catalina-luxury-apartments/</t>
         </is>
       </c>
     </row>
@@ -19148,6 +20008,11 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/villa-granada-santa-clara-ca/q89dqzw/</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
           <t>https://www.essexapartmenthomes.com/apartments/santa-clara/villa-granada</t>
         </is>
       </c>
@@ -19257,7 +20122,12 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>https://www.prometheusapartments.com/ca/santa-clara-apartments/cobalt</t>
+          <t>https://www.apartments.com/cobalt-santa-clara-ca/pnpkzps/</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/ca/santa-clara-apartments/cobalt</t>
         </is>
       </c>
     </row>
@@ -19366,7 +20236,12 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>https://www.hollandresidential.com/ca/santa-clara/orlo</t>
+          <t>https://www.apartments.com/orlo-and-alba-santa-clara-ca/1pw4vv6/</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hollandresidential.com/ca/santa-clara/orlo-alba</t>
         </is>
       </c>
     </row>
@@ -19475,6 +20350,11 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
+          <t>https://www.apartments.com/domicilio-santa-clara-ca/6x81pwt/</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
           <t>https://www.domicilioapts.com/</t>
         </is>
       </c>
@@ -19487,7 +20367,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Amara at Tasman East</t>
+          <t>Marina Playa Apartment Homes</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -19564,7 +20444,7 @@
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>Greystar (Verified Active Community (Greystar))</t>
+          <t>UDR (Verified Active Community (Greystar))</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
@@ -19579,12 +20459,17 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>2233 Calle Del Mundo, Santa Clara, CA 95054</t>
+          <t>3500 Granada Ave, Santa Clara, CA 95051</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>https://www.greystar.com/</t>
+          <t>https://www.apartments.com/marina-playa-santa-clara-ca/d6tg4dk/</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.udr.com/san-francisco-bay-area-apartments/santa-clara/marina-playa/</t>
         </is>
       </c>
     </row>
@@ -19690,12 +20575,17 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2250 Monroe St, Santa Clara, CA 95050</t>
+          <t>4500 Carlyle Ct, Santa Clara, CA 95054</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>https://www.apartments.com/the-carlyle-santa-clara-ca/</t>
+          <t>https://www.apartments.com/carlyle-santa-clara-ca/j7b5mj7/</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thecarlyle-apartments.com/</t>
         </is>
       </c>
     </row>

--- a/San_Jose_Apartments_Tracker.xlsx
+++ b/San_Jose_Apartments_Tracker.xlsx
@@ -10673,6 +10673,2880 @@
         </is>
       </c>
     </row>
+    <row r="93" ht="42" customHeight="1">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Nantucket Apartments</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Santa Clara (SVP Utility)</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>2.5 Mi to Cisco + SVP Power + $0 Park</t>
+        </is>
+      </c>
+      <c r="E93" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="F93" s="3">
+        <v>9</v>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>17m total (5m walk → 7m VTA Orange Line → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J93" s="3">
+        <v>3150</v>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>735–856</t>
+        </is>
+      </c>
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>Silicon Valley Power (~$0.18/kWh — 60% cheaper!)</t>
+        </is>
+      </c>
+      <c r="N93" s="3">
+        <v>120</v>
+      </c>
+      <c r="O93" s="3">
+        <v>3270</v>
+      </c>
+      <c r="P93" s="3">
+        <v>3270</v>
+      </c>
+      <c r="Q93" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R93" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S93" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T93" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="U93" s="3" t="inlineStr">
+        <is>
+          <t>AMC (Apartment Management Consultants) (Verified Market-Rate Garden Community)</t>
+        </is>
+      </c>
+      <c r="V93" s="3" t="inlineStr">
+        <is>
+          <t>Only 2.5 miles down Tasman Dr to Cisco HQ; includes $0 covered parking and 60% cheaper Santa Clara Silicon Valley Power electricity (~$120/mo summer A/C savings).</t>
+        </is>
+      </c>
+      <c r="W93" s="3" t="inlineStr">
+        <is>
+          <t>Levi's Stadium event days can bring temporary traffic along Great America Pkwy; older 1980s exterior framing (interiors renovated).</t>
+        </is>
+      </c>
+      <c r="X93" s="3" t="inlineStr">
+        <is>
+          <t>1600 Nantucket Cir, Santa Clara, CA 95054</t>
+        </is>
+      </c>
+      <c r="Y93" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/nantucket-santa-clara-ca/fjmjsrv/</t>
+        </is>
+      </c>
+      <c r="Z93" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nantucket-apartments.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="42" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Park Central Apartments</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Santa Clara (SVP Utility)</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>8 Weeks Free (-$515/mo) + SVP + $0 Park</t>
+        </is>
+      </c>
+      <c r="E94" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>11</v>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>29m total (6m walk → 18m VTA Bus 60 North → VTA Blue Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J94" s="3">
+        <v>3350</v>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>662–740</t>
+        </is>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>Silicon Valley Power (~$0.18/kWh — 60% cheaper!)</t>
+        </is>
+      </c>
+      <c r="N94" s="3">
+        <v>125</v>
+      </c>
+      <c r="O94" s="3">
+        <v>3475</v>
+      </c>
+      <c r="P94" s="3">
+        <v>3475</v>
+      </c>
+      <c r="Q94" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R94" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S94" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T94" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="U94" s="3" t="inlineStr">
+        <is>
+          <t>Prometheus Real Estate Group (Verified Institutional Manager (Prometheus))</t>
+        </is>
+      </c>
+      <c r="V94" s="3" t="inlineStr">
+        <is>
+          <t>Up to 8 weeks free rent (-$515/mo credit) drops net effective rent to ~$2,835/mo, plus $0 free parking and cheap Santa Clara SVP electricity!</t>
+        </is>
+      </c>
+      <c r="W94" s="3" t="inlineStr">
+        <is>
+          <t>Higher base sticker rent after year-1 concession expires; visitor parking requires permit.</t>
+        </is>
+      </c>
+      <c r="X94" s="3" t="inlineStr">
+        <is>
+          <t>1050 Benton St, Santa Clara, CA 95050</t>
+        </is>
+      </c>
+      <c r="Y94" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/park-central-santa-clara-ca/9hj8bj5/</t>
+        </is>
+      </c>
+      <c r="Z94" s="3" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/apartments/ca/santa-clara/park-central/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="42" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Hearth Apartments</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Santa Clara (SVP Utility)</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Steps to Central Park + SVP Power + $0 Park</t>
+        </is>
+      </c>
+      <c r="E95" s="2">
+        <v>6.4</v>
+      </c>
+      <c r="F95" s="2">
+        <v>13</v>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>29m total (3m walk → 21m VTA Bus 57 North → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J95" s="2">
+        <v>3450</v>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>686–751</t>
+        </is>
+      </c>
+      <c r="L95" s="2">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>Silicon Valley Power (~$0.18/kWh — 60% cheaper!)</t>
+        </is>
+      </c>
+      <c r="N95" s="2">
+        <v>125</v>
+      </c>
+      <c r="O95" s="2">
+        <v>3575</v>
+      </c>
+      <c r="P95" s="2">
+        <v>3575</v>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T95" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>Prometheus Real Estate Group (Verified Institutional Manager (Prometheus))</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>Walkable to Santa Clara Central Park, library, and Safeway; includes $0 free parking, cheap SVP electricity, and up to 3 weeks free.</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>Near the $3,450 top of the budget range before applying the 3-weeks-free special.</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>2870 Kaiser Dr, Santa Clara, CA 95051</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/hearth-santa-clara-ca/jmgnhs6/</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/apartments/ca/santa-clara/hearth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="42" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>The Benton</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Santa Clara (SVP Utility)</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>2021 Rooftop Saltwater Pool + SVP Power</t>
+        </is>
+      </c>
+      <c r="E96" s="2">
+        <v>4.9</v>
+      </c>
+      <c r="F96" s="2">
+        <v>10</v>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>28m total (5m walk → 18m VTA Bus 60 North → VTA Blue Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J96" s="2">
+        <v>3475</v>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>755–913</t>
+        </is>
+      </c>
+      <c r="L96" s="2">
+        <v>100</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>Silicon Valley Power (~$0.18/kWh — 60% cheaper!)</t>
+        </is>
+      </c>
+      <c r="N96" s="2">
+        <v>130</v>
+      </c>
+      <c r="O96" s="2">
+        <v>3705</v>
+      </c>
+      <c r="P96" s="2">
+        <v>3705</v>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T96" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>Prometheus Real Estate Group (Verified 2021 Luxury Build (Prometheus))</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>Newer 2021 luxury construction with large 755–913 sq ft 1BR layouts, rooftop saltwater pool, and cheap Santa Clara SVP electric rates.</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>Sits at the top of the $3,500 base budget cap with $100/mo parking; request an interior courtyard unit away from El Camino Real.</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>588 El Camino Real, Santa Clara, CA 95050</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-benton-santa-clara-ca/dxh36kl/</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/apartments/ca/santa-clara/the-benton/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="42" customHeight="1">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>The Luxe Apartments</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Santa Clara (SVP Utility)</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>1BR at $2,595 + SVP Power + $0 Garage</t>
+        </is>
+      </c>
+      <c r="E97" s="3">
+        <v>8.4</v>
+      </c>
+      <c r="F97" s="3">
+        <v>16</v>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>32m total (3m walk → 24m VTA Bus 57 North → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H97" s="3">
+        <v>2395</v>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>450–520</t>
+        </is>
+      </c>
+      <c r="J97" s="3">
+        <v>2595</v>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>650–720</t>
+        </is>
+      </c>
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>Silicon Valley Power (~$0.18/kWh — 60% cheaper!)</t>
+        </is>
+      </c>
+      <c r="N97" s="3">
+        <v>115</v>
+      </c>
+      <c r="O97" s="3">
+        <v>2510</v>
+      </c>
+      <c r="P97" s="3">
+        <v>2710</v>
+      </c>
+      <c r="Q97" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R97" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S97" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T97" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="U97" s="3" t="inlineStr">
+        <is>
+          <t>Spieker Companies (Verified Market-Rate Community (Spieker))</t>
+        </is>
+      </c>
+      <c r="V97" s="3" t="inlineStr">
+        <is>
+          <t>Rare sub-$2,600 1BR ($2,595) and $2,395 Studio in Santa Clara with $0 underground garage parking, In-Unit W/D, Central A/C, and cheap SVP electricity!</t>
+        </is>
+      </c>
+      <c r="W97" s="3" t="inlineStr">
+        <is>
+          <t>14-minute commute up Lawrence Expy -&gt; Hwy 237 E to Cisco; finishes are clean and functional rather than ultra-high-rise luxury.</t>
+        </is>
+      </c>
+      <c r="X97" s="3" t="inlineStr">
+        <is>
+          <t>3301 Homestead Rd, Santa Clara, CA 95051</t>
+        </is>
+      </c>
+      <c r="Y97" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-luxe-santa-clara-ca/58bdlkm/</t>
+        </is>
+      </c>
+      <c r="Z97" s="3" t="inlineStr">
+        <is>
+          <t>https://www.theluxeapartments.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="42" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Boardwalk at The Lakes</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Santa Clara (SVP Utility)</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>$2,650 Studio + Waterfront Lagoons + SVP</t>
+        </is>
+      </c>
+      <c r="E98" s="2">
+        <v>7.1</v>
+      </c>
+      <c r="F98" s="2">
+        <v>14</v>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>30m total (4m walk → 21m VTA Bus 57 North → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H98" s="2">
+        <v>2650</v>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="J98" s="2">
+        <v>3295</v>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>700–750</t>
+        </is>
+      </c>
+      <c r="L98" s="2">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>Silicon Valley Power (~$0.18/kWh — 60% cheaper!)</t>
+        </is>
+      </c>
+      <c r="N98" s="2">
+        <v>120</v>
+      </c>
+      <c r="O98" s="2">
+        <v>2770</v>
+      </c>
+      <c r="P98" s="2">
+        <v>3415</v>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T98" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>Prometheus Real Estate Group (Verified Institutional Manager (Prometheus))</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>Unique waterfront lagoon setting with studios at $2,650, $0 included parking, responsive Prometheus maintenance, and cheap Santa Clara SVP electricity.</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>Resident ducks around the waterways leave droppings on paths; studios are compact.</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>3770 Flora Vista Ave, Santa Clara, CA 95051</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/boardwalk-santa-clara-ca/gx12z2y/</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/apartments/ca/santa-clara/boardwalk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="42" customHeight="1">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>The Deck Apartment Homes</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Santa Clara (SVP Utility)</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>2024 Build + Rooftop Pool + SVP + $0 Park</t>
+        </is>
+      </c>
+      <c r="E99" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="F99" s="3">
+        <v>13</v>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>29m total (3m walk → 21m VTA Bus 57 North → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J99" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>728–780</t>
+        </is>
+      </c>
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>Silicon Valley Power (~$0.18/kWh — 60% cheaper!)</t>
+        </is>
+      </c>
+      <c r="N99" s="3">
+        <v>120</v>
+      </c>
+      <c r="O99" s="3">
+        <v>3520</v>
+      </c>
+      <c r="P99" s="3">
+        <v>3520</v>
+      </c>
+      <c r="Q99" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R99" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S99" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T99" s="3">
+        <v>4.1</v>
+      </c>
+      <c r="U99" s="3" t="inlineStr">
+        <is>
+          <t>De Anza Properties (Verified 2024 Luxury Build (De Anza Properties))</t>
+        </is>
+      </c>
+      <c r="V99" s="3" t="inlineStr">
+        <is>
+          <t>Brand-new 2024 build with a rooftop heated pool, $0 included structured garage parking, cheap Santa Clara SVP electricity, and strict no-pets policy (spotless common areas!).</t>
+        </is>
+      </c>
+      <c r="W99" s="3" t="inlineStr">
+        <is>
+          <t>Base 1BR rent starts at $3,400; select an interior-facing unit away from El Camino Real.</t>
+        </is>
+      </c>
+      <c r="X99" s="3" t="inlineStr">
+        <is>
+          <t>3406 El Camino Real, Santa Clara, CA 95051</t>
+        </is>
+      </c>
+      <c r="Y99" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-deck-santa-clara-ca/3x5w42f/</t>
+        </is>
+      </c>
+      <c r="Z99" s="3" t="inlineStr">
+        <is>
+          <t>https://www.deanzaproperties.com/thedeck</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="42" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Gideon at The Fields</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Milpitas Corridor</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Rooftop Pool + Trader Joe's On-Site (2.4 Mi)</t>
+        </is>
+      </c>
+      <c r="E100" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="F100" s="2">
+        <v>7</v>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>15m total (5m walk → 5m VTA Orange Line → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H100" s="2">
+        <v>3195</v>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>511–650</t>
+        </is>
+      </c>
+      <c r="J100" s="2">
+        <v>3450</v>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>744–855</t>
+        </is>
+      </c>
+      <c r="L100" s="2">
+        <v>75</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N100" s="2">
+        <v>215</v>
+      </c>
+      <c r="O100" s="2">
+        <v>3485</v>
+      </c>
+      <c r="P100" s="2">
+        <v>3740</v>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T100" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>Lyon Living (Verified Master-Planned Community (The Fields))</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>Sister building to Turing at The Fields with Trader Joe's, Starbucks, and OrangeTheory right downstairs; 6-minute drive down Tasman Dr to Cisco HQ.</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>Unbundled $75/mo parking and utility pass-through fees; choose a top-floor unit to avoid upstairs footstep noise.</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>150 Market St, Milpitas, CA 95035</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/gideon-milpitas-ca/45194kl/</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.livethefields.com/gideon</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="42" customHeight="1">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>Graham at The Fields</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Milpitas Corridor</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>Trader Joe's On-Site + $0 Free Parking</t>
+        </is>
+      </c>
+      <c r="E101" s="3">
+        <v>2.6</v>
+      </c>
+      <c r="F101" s="3">
+        <v>7</v>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>15m total (5m walk → 5m VTA Orange Line → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H101" s="3">
+        <v>3170</v>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="J101" s="3">
+        <v>3410</v>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>717–1076</t>
+        </is>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N101" s="3">
+        <v>215</v>
+      </c>
+      <c r="O101" s="3">
+        <v>3385</v>
+      </c>
+      <c r="P101" s="3">
+        <v>3625</v>
+      </c>
+      <c r="Q101" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R101" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S101" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T101" s="3">
+        <v>3.7</v>
+      </c>
+      <c r="U101" s="3" t="inlineStr">
+        <is>
+          <t>Lyon Living (Verified Master-Planned Community (The Fields))</t>
+        </is>
+      </c>
+      <c r="V101" s="3" t="inlineStr">
+        <is>
+          <t>Unlike Turing and Gideon next door, Graham includes your 1st garage parking space FREE ($0/mo) while still giving you Trader Joe's downstairs and a 6-min drive to Cisco!</t>
+        </is>
+      </c>
+      <c r="W101" s="3" t="inlineStr">
+        <is>
+          <t>Strict visitor parking rules; standard Lyon Living move-out cleaning deductions.</t>
+        </is>
+      </c>
+      <c r="X101" s="3" t="inlineStr">
+        <is>
+          <t>1415 McCandless Dr, Milpitas, CA 95035</t>
+        </is>
+      </c>
+      <c r="Y101" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/graham-at-the-fields-milpitas-ca/6xnnf5v/</t>
+        </is>
+      </c>
+      <c r="Z101" s="3" t="inlineStr">
+        <is>
+          <t>https://www.livethefields.com/graham</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="42" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>The Hazelwood Apartments</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Milpitas Corridor</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>720 Sq Ft 1BR at $2,700 + $0 Parking</t>
+        </is>
+      </c>
+      <c r="E102" s="2">
+        <v>4.6</v>
+      </c>
+      <c r="F102" s="2">
+        <v>10</v>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>26m total (3m walk → 18m VTA Bus 66 South → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H102" s="2">
+        <v>2360</v>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>310–410</t>
+        </is>
+      </c>
+      <c r="J102" s="2">
+        <v>2700</v>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="L102" s="2">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N102" s="2">
+        <v>200</v>
+      </c>
+      <c r="O102" s="2">
+        <v>2560</v>
+      </c>
+      <c r="P102" s="2">
+        <v>2900</v>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T102" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>Klingbeil Capital Management (Verified Renovated Garden Community)</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>True 720 sq ft 1-Bedroom starting at $2,700/mo (and micro-studios at $2,360) with $0 covered parking, Ecobee central A/C, and in-unit W/D just 9 minutes down I-880 S to Cisco!</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>Studio layout ('The Lily') is micro-sized — opt for the 720 sq ft 1BR ('The Poppy') at $2,700 instead.</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>2021 N Milpitas Blvd, Milpitas, CA 95035</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-hazelwood-milpitas-ca/cv309he/</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thehazelwoodapts.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="42" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>The James</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Japantown &amp; Downtown</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>4.0★ Direct VTA Blue Line at Doorstep</t>
+        </is>
+      </c>
+      <c r="E103" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="F103" s="2">
+        <v>13</v>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>23m total (2m walk → 16m VTA Blue Line → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H103" s="2">
+        <v>3056</v>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>575–654</t>
+        </is>
+      </c>
+      <c r="J103" s="2">
+        <v>3280</v>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>676–1170</t>
+        </is>
+      </c>
+      <c r="L103" s="2">
+        <v>125</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N103" s="2">
+        <v>215</v>
+      </c>
+      <c r="O103" s="2">
+        <v>3396</v>
+      </c>
+      <c r="P103" s="2">
+        <v>3620</v>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T103" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>North Coast Living (Virtu Investments) (Verified Modern Luxury Community)</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>VTA Blue Line boards right outside on N 1st St for a direct train ride to Cisco Way Station; sleek modern interiors 2 blocks from San Pedro Square.</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>St. James Park across the street has unhoused street activity; unbundled $125/mo garage parking.</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>98 N 1st St, San Jose, CA 95113</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-james-san-jose-ca/pyd13kv/</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jamesliving.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="42" customHeight="1">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>Foundry Commons</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Japantown &amp; Downtown</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>4.2★ Studio $2,300 / 1BR $2,850 + 6 Wks Free</t>
+        </is>
+      </c>
+      <c r="E104" s="3">
+        <v>7.9</v>
+      </c>
+      <c r="F104" s="3">
+        <v>15</v>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>31m total (6m walk → 20m VTA Blue Line → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H104" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="J104" s="3">
+        <v>2850</v>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>690–726</t>
+        </is>
+      </c>
+      <c r="L104" s="3">
+        <v>75</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N104" s="3">
+        <v>210</v>
+      </c>
+      <c r="O104" s="3">
+        <v>2585</v>
+      </c>
+      <c r="P104" s="3">
+        <v>3135</v>
+      </c>
+      <c r="Q104" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R104" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S104" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T104" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="U104" s="3" t="inlineStr">
+        <is>
+          <t>Greystar (Verified Institutional Manager (Greystar))</t>
+        </is>
+      </c>
+      <c r="V104" s="3" t="inlineStr">
+        <is>
+          <t>4.2★ Greystar community where BOTH 560 sq ft Studios ($2,300) and 690–726 sq ft 1BRs ($2,850) start well under $3,000 with 6–8 weeks free specials!</t>
+        </is>
+      </c>
+      <c r="W104" s="3" t="inlineStr">
+        <is>
+          <t>Limited street guest parking; industrial/residential fringe south of SJSU.</t>
+        </is>
+      </c>
+      <c r="X104" s="3" t="inlineStr">
+        <is>
+          <t>868 S 5th St, San Jose, CA 95112</t>
+        </is>
+      </c>
+      <c r="Y104" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/foundry-commons-san-jose-ca/v7v04xe/</t>
+        </is>
+      </c>
+      <c r="Z104" s="3" t="inlineStr">
+        <is>
+          <t>https://www.foundrycommonsapts.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="42" customHeight="1">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>Avalon at Cahill Park</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Midtown &amp; West SJ</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>4.3★ AvalonBay Across from Whole Foods</t>
+        </is>
+      </c>
+      <c r="E105" s="3">
+        <v>6.9</v>
+      </c>
+      <c r="F105" s="3">
+        <v>13</v>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>30m total (4m walk → 21m VTA Green → Blue Line → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J105" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>712–991</t>
+        </is>
+      </c>
+      <c r="L105" s="3">
+        <v>100</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N105" s="3">
+        <v>210</v>
+      </c>
+      <c r="O105" s="3">
+        <v>3410</v>
+      </c>
+      <c r="P105" s="3">
+        <v>3410</v>
+      </c>
+      <c r="Q105" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R105" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S105" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T105" s="3">
+        <v>4.3</v>
+      </c>
+      <c r="U105" s="3" t="inlineStr">
+        <is>
+          <t>AvalonBay Communities (Verified Institutional REIT (AvalonBay))</t>
+        </is>
+      </c>
+      <c r="V105" s="3" t="inlineStr">
+        <is>
+          <t>4.3★ AvalonBay flagship right across from Whole Foods Market, Cahill Park, and Diridon Station with spacious 712–991 sq ft 1BR floor plans.</t>
+        </is>
+      </c>
+      <c r="W105" s="3" t="inlineStr">
+        <is>
+          <t>Caltrain/SAP Center activity nearby; $100/mo parking fee.</t>
+        </is>
+      </c>
+      <c r="X105" s="3" t="inlineStr">
+        <is>
+          <t>754 The Alameda, San Jose, CA 95126</t>
+        </is>
+      </c>
+      <c r="Y105" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/avalon-at-cahill-park-san-jose-ca/1krpwp7/</t>
+        </is>
+      </c>
+      <c r="Z105" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avaloncommunities.com/california/san-jose-apartments/avalon-at-cahill-park/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="42" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Mosaic Apartments</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Midtown &amp; West SJ</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Huge 861–920 Sq Ft 1BRs + Steps to VTA</t>
+        </is>
+      </c>
+      <c r="E106" s="2">
+        <v>7.7</v>
+      </c>
+      <c r="F106" s="2">
+        <v>14</v>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>32m total (3m walk → 24m VTA Green → Blue Line → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J106" s="2">
+        <v>3340</v>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>861–920</t>
+        </is>
+      </c>
+      <c r="L106" s="2">
+        <v>75</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N106" s="2">
+        <v>215</v>
+      </c>
+      <c r="O106" s="2">
+        <v>3630</v>
+      </c>
+      <c r="P106" s="2">
+        <v>3630</v>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T106" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>Greystar (Verified Institutional Manager (Greystar))</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>Massive 861–920 sq ft 1-Bedroom floor plans (nearly 200 sq ft larger than typical studios/1BRs) with 4–6 weeks free specials and steps from Race VTA!</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>Unbundled $75/mo parking and utility pass-throughs; street noise on Race St-facing balconies.</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>500 Race St, San Jose, CA 95126</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/mosaic-apartments-san-jose-ca/lnvdq4e/</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.liveatmosaicapts.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="42" customHeight="1">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>Artis Willow Glen (Silver)</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Midtown &amp; West SJ</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Studio $2,875 / 1BR $2,995 + 6 Wks Free</t>
+        </is>
+      </c>
+      <c r="E107" s="3">
+        <v>7.7</v>
+      </c>
+      <c r="F107" s="3">
+        <v>13</v>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>34m total (5m walk → 24m VTA Green → Blue Line → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H107" s="3">
+        <v>2875</v>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>523–614</t>
+        </is>
+      </c>
+      <c r="J107" s="3">
+        <v>2995</v>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>666–982</t>
+        </is>
+      </c>
+      <c r="L107" s="3">
+        <v>150</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N107" s="3">
+        <v>215</v>
+      </c>
+      <c r="O107" s="3">
+        <v>3240</v>
+      </c>
+      <c r="P107" s="3">
+        <v>3360</v>
+      </c>
+      <c r="Q107" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R107" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S107" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T107" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="U107" s="3" t="inlineStr">
+        <is>
+          <t>Greystar (Verified Institutional Manager (Greystar))</t>
+        </is>
+      </c>
+      <c r="V107" s="3" t="inlineStr">
+        <is>
+          <t>Both Studios ($2,875) and entry 1BRs ($2,995) start under $3,000 right next to Del Monte Park and Los Gatos Creek Trail, plus up to 6 weeks free!</t>
+        </is>
+      </c>
+      <c r="W107" s="3" t="inlineStr">
+        <is>
+          <t>$150/mo garage parking fee; Caltrain tracks run behind the eastern edge of the property.</t>
+        </is>
+      </c>
+      <c r="X107" s="3" t="inlineStr">
+        <is>
+          <t>333 Sunol St, San Jose, CA 95126</t>
+        </is>
+      </c>
+      <c r="Y107" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/artis-willow-glen-san-jose-ca/m0q63fl/</t>
+        </is>
+      </c>
+      <c r="Z107" s="3" t="inlineStr">
+        <is>
+          <t>https://www.silversj.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="42" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Santana Row Living (Santana Heights)</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Midtown &amp; West SJ</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Live Directly Above Santana Row Dining</t>
+        </is>
+      </c>
+      <c r="E108" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="F108" s="2">
+        <v>15</v>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>35m total (3m walk → 27m VTA Bus 60 North → VTA Blue Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J108" s="2">
+        <v>3450</v>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>818–890</t>
+        </is>
+      </c>
+      <c r="L108" s="2">
+        <v>100</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N108" s="2">
+        <v>220</v>
+      </c>
+      <c r="O108" s="2">
+        <v>3770</v>
+      </c>
+      <c r="P108" s="2">
+        <v>3770</v>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T108" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>Federal Realty Investment Trust (Verified Institutional REIT (Federal Realty))</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>Unmatched social/dining lifestyle — take your elevator straight down to Santana Row's 30+ restaurants, bars, CineArts theater, and Valley Fair.</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>Top of the $3,500 budget cap; weekend shopping crowds and nightlife energy outside.</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>355 Santana Row, San Jose, CA 95128</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/santana-row-san-jose-ca/8s4byt3/</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.santanarow.com/living</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="42" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Misora at Santana Row</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Midtown &amp; West SJ</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>2 Pools on Santana Row + Up to 6 Wks Free</t>
+        </is>
+      </c>
+      <c r="E109" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="F109" s="2">
+        <v>15</v>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>35m total (3m walk → 27m VTA Bus 60 North → VTA Blue Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H109" s="2">
+        <v>3450</v>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>552–560</t>
+        </is>
+      </c>
+      <c r="J109" s="2">
+        <v>3495</v>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>753–1019</t>
+        </is>
+      </c>
+      <c r="L109" s="2">
+        <v>100</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N109" s="2">
+        <v>220</v>
+      </c>
+      <c r="O109" s="2">
+        <v>3770</v>
+      </c>
+      <c r="P109" s="2">
+        <v>3815</v>
+      </c>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S109" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T109" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="U109" s="2" t="inlineStr">
+        <is>
+          <t>Waterton (Verified Ultra-Luxury Community (Waterton))</t>
+        </is>
+      </c>
+      <c r="V109" s="2" t="inlineStr">
+        <is>
+          <t>Ultra-luxury Santana Row living with two pools, Roman soaking tubs, and up to 6 weeks free (-$395/mo) bringing net studio rent near ~$3,055/mo.</t>
+        </is>
+      </c>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
+          <t>High sticker price after year-1 concession; busy Santana Row weekend traffic.</t>
+        </is>
+      </c>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>388 Santana Row, San Jose, CA 95128</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/misora-san-jose-ca/y167ynt/</t>
+        </is>
+      </c>
+      <c r="Z109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.misoraluxuryapts.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="42" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Levare at Santana Row</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Midtown &amp; West SJ</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>4.2★ Highest-Rated Santana Row Building</t>
+        </is>
+      </c>
+      <c r="E110" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="F110" s="2">
+        <v>15</v>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>35m total (3m walk → 27m VTA Bus 60 North → VTA Blue Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J110" s="2">
+        <v>3490</v>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>748–1021</t>
+        </is>
+      </c>
+      <c r="L110" s="2">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N110" s="2">
+        <v>220</v>
+      </c>
+      <c r="O110" s="2">
+        <v>3710</v>
+      </c>
+      <c r="P110" s="2">
+        <v>3710</v>
+      </c>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R110" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S110" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T110" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="U110" s="2" t="inlineStr">
+        <is>
+          <t>Greystar (Verified Boutique Luxury Community (Greystar))</t>
+        </is>
+      </c>
+      <c r="V110" s="2" t="inlineStr">
+        <is>
+          <t>4.2★ highest-rated building at Santana Row with quieter boutique concrete construction, Bosch appliances, and 10–12 ft ceilings.</t>
+        </is>
+      </c>
+      <c r="W110" s="2" t="inlineStr">
+        <is>
+          <t>Sits right at the $3,490 budget ceiling; weekend congestion along Olin Ave and Winchester Blvd.</t>
+        </is>
+      </c>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>3003 Olin Ave, San Jose, CA 95128</t>
+        </is>
+      </c>
+      <c r="Y110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/levare-san-jose-ca/mspmc1j/</t>
+        </is>
+      </c>
+      <c r="Z110" s="2" t="inlineStr">
+        <is>
+          <t>https://levareliving.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="42" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Avana Sunnyvale</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale &amp; Campbell</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Huge 800–870 Sq Ft 1BRs in Sunnyvale</t>
+        </is>
+      </c>
+      <c r="E111" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="F111" s="2">
+        <v>13</v>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>26m total (8m walk → 13m VTA Orange Line → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J111" s="2">
+        <v>3300</v>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>800–870</t>
+        </is>
+      </c>
+      <c r="L111" s="2">
+        <v>75</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N111" s="2">
+        <v>210</v>
+      </c>
+      <c r="O111" s="2">
+        <v>3585</v>
+      </c>
+      <c r="P111" s="2">
+        <v>3585</v>
+      </c>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R111" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S111" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T111" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="U111" s="2" t="inlineStr">
+        <is>
+          <t>Greystar (Verified Institutional Manager (Greystar))</t>
+        </is>
+      </c>
+      <c r="V111" s="2" t="inlineStr">
+        <is>
+          <t>Very large 800–870 sq ft 1-Bedroom floor plans on N Wolfe Rd with a quick 10-minute commute via US-101 S / Tasman Dr to Cisco HQ.</t>
+        </is>
+      </c>
+      <c r="W111" s="2" t="inlineStr">
+        <is>
+          <t>Unbundled $75/mo parking fee; Wolfe Rd commuter traffic during peak hours.</t>
+        </is>
+      </c>
+      <c r="X111" s="2" t="inlineStr">
+        <is>
+          <t>355 N Wolfe Rd, Sunnyvale, CA 94085</t>
+        </is>
+      </c>
+      <c r="Y111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/avana-sunnyvale-sunnyvale-ca/0r08j30/</t>
+        </is>
+      </c>
+      <c r="Z111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avanasunnyvale.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="42" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>The Murphy Station</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale &amp; Campbell</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>2022 Sunnyvale Build + $0 Garage Parking</t>
+        </is>
+      </c>
+      <c r="E112" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="F112" s="2">
+        <v>17</v>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>29m total (3m walk → 21m VTA Bus 56 North → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H112" s="2">
+        <v>3040</v>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="J112" s="2">
+        <v>3450</v>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>769–788</t>
+        </is>
+      </c>
+      <c r="L112" s="2">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N112" s="2">
+        <v>210</v>
+      </c>
+      <c r="O112" s="2">
+        <v>3250</v>
+      </c>
+      <c r="P112" s="2">
+        <v>3660</v>
+      </c>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R112" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S112" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T112" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="U112" s="2" t="inlineStr">
+        <is>
+          <t>St. Anton Multifamily (Verified 2022 Luxury Mid-Rise)</t>
+        </is>
+      </c>
+      <c r="V112" s="2" t="inlineStr">
+        <is>
+          <t>Newer 2022 5-story construction in Sunnyvale with $0 included underground garage parking, keyless entry, and rooftop fireplace terrace.</t>
+        </is>
+      </c>
+      <c r="W112" s="2" t="inlineStr">
+        <is>
+          <t>Request a north/courtyard-facing unit away from El Camino Real traffic noise.</t>
+        </is>
+      </c>
+      <c r="X112" s="2" t="inlineStr">
+        <is>
+          <t>1008 E El Camino Real, Sunnyvale, CA 94087</t>
+        </is>
+      </c>
+      <c r="Y112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-murphy-station-sunnyvale-ca/6vw7vwv/</t>
+        </is>
+      </c>
+      <c r="Z112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.murphystationapts.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="42" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>The Maddox Sunnyvale</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale &amp; Campbell</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Sub-$3,000 Sunnyvale Studio + $0 Parking</t>
+        </is>
+      </c>
+      <c r="E113" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="F113" s="2">
+        <v>20</v>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>30m total (3m walk → 22m VTA Bus 56 North → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H113" s="2">
+        <v>2920</v>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="J113" s="2">
+        <v>3320</v>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>712–733</t>
+        </is>
+      </c>
+      <c r="L113" s="2">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N113" s="2">
+        <v>205</v>
+      </c>
+      <c r="O113" s="2">
+        <v>3125</v>
+      </c>
+      <c r="P113" s="2">
+        <v>3525</v>
+      </c>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S113" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T113" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="U113" s="2" t="inlineStr">
+        <is>
+          <t>IEC Property Services (Verified Market-Rate Community (IEC))</t>
+        </is>
+      </c>
+      <c r="V113" s="2" t="inlineStr">
+        <is>
+          <t>Sub-$3,000 Sunnyvale Studio ($2,920) and $3,320 1BR with $0 covered parking, Central A/C, and In-Unit W/D right along Sunnyvale's best dining strip.</t>
+        </is>
+      </c>
+      <c r="W113" s="2" t="inlineStr">
+        <is>
+          <t>Late-1980s building framing (renovated interiors); pick a courtyard unit away from El Camino Real.</t>
+        </is>
+      </c>
+      <c r="X113" s="2" t="inlineStr">
+        <is>
+          <t>874 E El Camino Real, Sunnyvale, CA 94087</t>
+        </is>
+      </c>
+      <c r="Y113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-maddox-sunnyvale-sunnyvale-ca/h4yw0y1/</t>
+        </is>
+      </c>
+      <c r="Z113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.maddoxsunnyvaleapartments.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="42" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Ironworks Apartments</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale &amp; Campbell</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Walk to Downtown Sunnyvale Murphy Ave</t>
+        </is>
+      </c>
+      <c r="E114" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="F114" s="2">
+        <v>15</v>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>30m total (5m walk → 20m VTA Bus 55 North → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J114" s="2">
+        <v>3475</v>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>750–840</t>
+        </is>
+      </c>
+      <c r="L114" s="2">
+        <v>75</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N114" s="2">
+        <v>215</v>
+      </c>
+      <c r="O114" s="2">
+        <v>3765</v>
+      </c>
+      <c r="P114" s="2">
+        <v>3765</v>
+      </c>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R114" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S114" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T114" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="U114" s="2" t="inlineStr">
+        <is>
+          <t>Prometheus Real Estate Group (Verified Institutional Manager (Prometheus))</t>
+        </is>
+      </c>
+      <c r="V114" s="2" t="inlineStr">
+        <is>
+          <t>Steps from Downtown Sunnyvale's Murphy Ave restaurants, Target, Whole Foods, and Caltrain with modern Prometheus finishes and a rooftop lounge.</t>
+        </is>
+      </c>
+      <c r="W114" s="2" t="inlineStr">
+        <is>
+          <t>Caltrain tracks run along Evelyn Ave (request a courtyard-facing unit); sits near the $3,500 budget cap.</t>
+        </is>
+      </c>
+      <c r="X114" s="2" t="inlineStr">
+        <is>
+          <t>457 E Evelyn Ave, Sunnyvale, CA 94086</t>
+        </is>
+      </c>
+      <c r="Y114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/ironworks-sunnyvale-ca/pqr7qwv/</t>
+        </is>
+      </c>
+      <c r="Z114" s="2" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/ca/sunnyvale-apartments/ironworks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="42" customHeight="1">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>481 on Mathilda</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Sunnyvale &amp; Campbell</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>4.2★ 3 Blocks to Sunnyvale Whole Foods &amp; AMC</t>
+        </is>
+      </c>
+      <c r="E115" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="F115" s="3">
+        <v>18</v>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>30m total (3m walk → 22m VTA Bus 55 North → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H115" s="3">
+        <v>3250</v>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>557–650</t>
+        </is>
+      </c>
+      <c r="J115" s="3">
+        <v>3495</v>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>745–791</t>
+        </is>
+      </c>
+      <c r="L115" s="3">
+        <v>75</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N115" s="3">
+        <v>215</v>
+      </c>
+      <c r="O115" s="3">
+        <v>3540</v>
+      </c>
+      <c r="P115" s="3">
+        <v>3785</v>
+      </c>
+      <c r="Q115" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R115" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S115" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T115" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="U115" s="3" t="inlineStr">
+        <is>
+          <t>Greystar (Verified Institutional Manager (Greystar))</t>
+        </is>
+      </c>
+      <c r="V115" s="3" t="inlineStr">
+        <is>
+          <t>4.2★ Greystar luxury just 3 blocks south of Downtown Sunnyvale's Whole Foods, Target, AMC dine-in theater, and Murphy Ave restaurants!</t>
+        </is>
+      </c>
+      <c r="W115" s="3" t="inlineStr">
+        <is>
+          <t>Mathilda Ave commuter traffic during rush hour; $75/mo parking fee.</t>
+        </is>
+      </c>
+      <c r="X115" s="3" t="inlineStr">
+        <is>
+          <t>481 S Mathilda Ave, Sunnyvale, CA 94086</t>
+        </is>
+      </c>
+      <c r="Y115" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/481-on-mathilda-sunnyvale-ca/tx88gtb/</t>
+        </is>
+      </c>
+      <c r="Z115" s="3" t="inlineStr">
+        <is>
+          <t>https://www.481onmathilda.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="42" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Citra Apartments</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale &amp; Campbell</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>580+ Sq Ft Studio + $0 Parking by Hwy 237</t>
+        </is>
+      </c>
+      <c r="E116" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="F116" s="2">
+        <v>16</v>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>33m total (4m walk → 24m VTA Rapid 523 → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H116" s="2">
+        <v>3150</v>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>580–626</t>
+        </is>
+      </c>
+      <c r="J116" s="2">
+        <v>3450</v>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>626–767</t>
+        </is>
+      </c>
+      <c r="L116" s="2">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N116" s="2">
+        <v>210</v>
+      </c>
+      <c r="O116" s="2">
+        <v>3360</v>
+      </c>
+      <c r="P116" s="2">
+        <v>3660</v>
+      </c>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S116" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T116" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="U116" s="2" t="inlineStr">
+        <is>
+          <t>Prime Residential (Verified Institutional Manager (Prime Residential))</t>
+        </is>
+      </c>
+      <c r="V116" s="2" t="inlineStr">
+        <is>
+          <t>Spacious 580–626 sq ft Studios ($3,150) and 1BRs ($3,450) with $0 included parking right by the Hwy 85 / Hwy 237 interchange for a straight freeway shot to Cisco.</t>
+        </is>
+      </c>
+      <c r="W116" s="2" t="inlineStr">
+        <is>
+          <t>Near the western edge of our 10-mile radius (~9.4 miles via Hwy 237 E).</t>
+        </is>
+      </c>
+      <c r="X116" s="2" t="inlineStr">
+        <is>
+          <t>745 S Bernardo Ave, Sunnyvale, CA 94087</t>
+        </is>
+      </c>
+      <c r="Y116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/citra-apartments-sunnyvale-ca/d71y2lh/</t>
+        </is>
+      </c>
+      <c r="Z116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.citrasunnyvale.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="42" customHeight="1">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>Naya Apartments</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Sunnyvale &amp; Campbell</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>4.3★ 2-Story Gym + Straight Hwy 237 Commute</t>
+        </is>
+      </c>
+      <c r="E117" s="3">
+        <v>9.8</v>
+      </c>
+      <c r="F117" s="3">
+        <v>16</v>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>31m total (3m walk → 23m VTA Rapid 523 → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J117" s="3">
+        <v>3490</v>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>694–765</t>
+        </is>
+      </c>
+      <c r="L117" s="3">
+        <v>75</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N117" s="3">
+        <v>215</v>
+      </c>
+      <c r="O117" s="3">
+        <v>3780</v>
+      </c>
+      <c r="P117" s="3">
+        <v>3780</v>
+      </c>
+      <c r="Q117" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R117" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S117" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T117" s="3">
+        <v>4.3</v>
+      </c>
+      <c r="U117" s="3" t="inlineStr">
+        <is>
+          <t>Greystar (Verified Institutional Manager (Greystar))</t>
+        </is>
+      </c>
+      <c r="V117" s="3" t="inlineStr">
+        <is>
+          <t>4.3★ Greystar building with one of the best 2-story apartment gyms in Sunnyvale, strong soundproofing, and a straight 14-min commute on Hwy 237 E to Cisco.</t>
+        </is>
+      </c>
+      <c r="W117" s="3" t="inlineStr">
+        <is>
+          <t>Sits at the $3,490 base budget cap before applying lease specials; $75/mo underground parking.</t>
+        </is>
+      </c>
+      <c r="X117" s="3" t="inlineStr">
+        <is>
+          <t>1095 W El Camino Real, Sunnyvale, CA 94087</t>
+        </is>
+      </c>
+      <c r="Y117" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/naya-sunnyvale-ca/prdh34v/</t>
+        </is>
+      </c>
+      <c r="Z117" s="3" t="inlineStr">
+        <is>
+          <t>https://www.liveatnaya.com/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -17795,6 +20669,1498 @@
       <c r="Z62" s="2" t="inlineStr">
         <is>
           <t>https://www.thecarlyle-apartments.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="42" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Nantucket Apartments</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Santa Clara (SVP Utility)</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>2.5 Mi to Cisco + SVP Power + $0 Park</t>
+        </is>
+      </c>
+      <c r="E63" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="F63" s="3">
+        <v>9</v>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>17m total (5m walk → 7m VTA Orange Line → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J63" s="3">
+        <v>3150</v>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>735–856</t>
+        </is>
+      </c>
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>Silicon Valley Power (~$0.18/kWh — 60% cheaper!)</t>
+        </is>
+      </c>
+      <c r="N63" s="3">
+        <v>120</v>
+      </c>
+      <c r="O63" s="3">
+        <v>3270</v>
+      </c>
+      <c r="P63" s="3">
+        <v>3270</v>
+      </c>
+      <c r="Q63" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S63" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T63" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="U63" s="3" t="inlineStr">
+        <is>
+          <t>AMC (Apartment Management Consultants) (Verified Market-Rate Garden Community)</t>
+        </is>
+      </c>
+      <c r="V63" s="3" t="inlineStr">
+        <is>
+          <t>Only 2.5 miles down Tasman Dr to Cisco HQ; includes $0 covered parking and 60% cheaper Santa Clara Silicon Valley Power electricity (~$120/mo summer A/C savings).</t>
+        </is>
+      </c>
+      <c r="W63" s="3" t="inlineStr">
+        <is>
+          <t>Levi's Stadium event days can bring temporary traffic along Great America Pkwy; older 1980s exterior framing (interiors renovated).</t>
+        </is>
+      </c>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>1600 Nantucket Cir, Santa Clara, CA 95054</t>
+        </is>
+      </c>
+      <c r="Y63" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/nantucket-santa-clara-ca/fjmjsrv/</t>
+        </is>
+      </c>
+      <c r="Z63" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nantucket-apartments.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="42" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Park Central Apartments</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Santa Clara (SVP Utility)</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>8 Weeks Free (-$515/mo) + SVP + $0 Park</t>
+        </is>
+      </c>
+      <c r="E64" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F64" s="3">
+        <v>11</v>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>29m total (6m walk → 18m VTA Bus 60 North → VTA Blue Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J64" s="3">
+        <v>3350</v>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>662–740</t>
+        </is>
+      </c>
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>Silicon Valley Power (~$0.18/kWh — 60% cheaper!)</t>
+        </is>
+      </c>
+      <c r="N64" s="3">
+        <v>125</v>
+      </c>
+      <c r="O64" s="3">
+        <v>3475</v>
+      </c>
+      <c r="P64" s="3">
+        <v>3475</v>
+      </c>
+      <c r="Q64" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R64" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S64" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T64" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="U64" s="3" t="inlineStr">
+        <is>
+          <t>Prometheus Real Estate Group (Verified Institutional Manager (Prometheus))</t>
+        </is>
+      </c>
+      <c r="V64" s="3" t="inlineStr">
+        <is>
+          <t>Up to 8 weeks free rent (-$515/mo credit) drops net effective rent to ~$2,835/mo, plus $0 free parking and cheap Santa Clara SVP electricity!</t>
+        </is>
+      </c>
+      <c r="W64" s="3" t="inlineStr">
+        <is>
+          <t>Higher base sticker rent after year-1 concession expires; visitor parking requires permit.</t>
+        </is>
+      </c>
+      <c r="X64" s="3" t="inlineStr">
+        <is>
+          <t>1050 Benton St, Santa Clara, CA 95050</t>
+        </is>
+      </c>
+      <c r="Y64" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/park-central-santa-clara-ca/9hj8bj5/</t>
+        </is>
+      </c>
+      <c r="Z64" s="3" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/apartments/ca/santa-clara/park-central/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="42" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>The Luxe Apartments</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Santa Clara (SVP Utility)</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>1BR at $2,595 + SVP Power + $0 Garage</t>
+        </is>
+      </c>
+      <c r="E65" s="3">
+        <v>8.4</v>
+      </c>
+      <c r="F65" s="3">
+        <v>16</v>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>32m total (3m walk → 24m VTA Bus 57 North → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H65" s="3">
+        <v>2395</v>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>450–520</t>
+        </is>
+      </c>
+      <c r="J65" s="3">
+        <v>2595</v>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>650–720</t>
+        </is>
+      </c>
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>Silicon Valley Power (~$0.18/kWh — 60% cheaper!)</t>
+        </is>
+      </c>
+      <c r="N65" s="3">
+        <v>115</v>
+      </c>
+      <c r="O65" s="3">
+        <v>2510</v>
+      </c>
+      <c r="P65" s="3">
+        <v>2710</v>
+      </c>
+      <c r="Q65" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S65" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T65" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="U65" s="3" t="inlineStr">
+        <is>
+          <t>Spieker Companies (Verified Market-Rate Community (Spieker))</t>
+        </is>
+      </c>
+      <c r="V65" s="3" t="inlineStr">
+        <is>
+          <t>Rare sub-$2,600 1BR ($2,595) and $2,395 Studio in Santa Clara with $0 underground garage parking, In-Unit W/D, Central A/C, and cheap SVP electricity!</t>
+        </is>
+      </c>
+      <c r="W65" s="3" t="inlineStr">
+        <is>
+          <t>14-minute commute up Lawrence Expy -&gt; Hwy 237 E to Cisco; finishes are clean and functional rather than ultra-high-rise luxury.</t>
+        </is>
+      </c>
+      <c r="X65" s="3" t="inlineStr">
+        <is>
+          <t>3301 Homestead Rd, Santa Clara, CA 95051</t>
+        </is>
+      </c>
+      <c r="Y65" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-luxe-santa-clara-ca/58bdlkm/</t>
+        </is>
+      </c>
+      <c r="Z65" s="3" t="inlineStr">
+        <is>
+          <t>https://www.theluxeapartments.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="42" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Boardwalk at The Lakes</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Santa Clara (SVP Utility)</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>$2,650 Studio + Waterfront Lagoons + SVP</t>
+        </is>
+      </c>
+      <c r="E66" s="2">
+        <v>7.1</v>
+      </c>
+      <c r="F66" s="2">
+        <v>14</v>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>30m total (4m walk → 21m VTA Bus 57 North → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H66" s="2">
+        <v>2650</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="J66" s="2">
+        <v>3295</v>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>700–750</t>
+        </is>
+      </c>
+      <c r="L66" s="2">
+        <v>0</v>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>Silicon Valley Power (~$0.18/kWh — 60% cheaper!)</t>
+        </is>
+      </c>
+      <c r="N66" s="2">
+        <v>120</v>
+      </c>
+      <c r="O66" s="2">
+        <v>2770</v>
+      </c>
+      <c r="P66" s="2">
+        <v>3415</v>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T66" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>Prometheus Real Estate Group (Verified Institutional Manager (Prometheus))</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>Unique waterfront lagoon setting with studios at $2,650, $0 included parking, responsive Prometheus maintenance, and cheap Santa Clara SVP electricity.</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>Resident ducks around the waterways leave droppings on paths; studios are compact.</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>3770 Flora Vista Ave, Santa Clara, CA 95051</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/boardwalk-santa-clara-ca/gx12z2y/</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/apartments/ca/santa-clara/boardwalk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="42" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>The Deck Apartment Homes</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Santa Clara (SVP Utility)</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>2024 Build + Rooftop Pool + SVP + $0 Park</t>
+        </is>
+      </c>
+      <c r="E67" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="F67" s="3">
+        <v>13</v>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>29m total (3m walk → 21m VTA Bus 57 North → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J67" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>728–780</t>
+        </is>
+      </c>
+      <c r="L67" s="3">
+        <v>0</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>Silicon Valley Power (~$0.18/kWh — 60% cheaper!)</t>
+        </is>
+      </c>
+      <c r="N67" s="3">
+        <v>120</v>
+      </c>
+      <c r="O67" s="3">
+        <v>3520</v>
+      </c>
+      <c r="P67" s="3">
+        <v>3520</v>
+      </c>
+      <c r="Q67" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R67" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S67" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T67" s="3">
+        <v>4.1</v>
+      </c>
+      <c r="U67" s="3" t="inlineStr">
+        <is>
+          <t>De Anza Properties (Verified 2024 Luxury Build (De Anza Properties))</t>
+        </is>
+      </c>
+      <c r="V67" s="3" t="inlineStr">
+        <is>
+          <t>Brand-new 2024 build with a rooftop heated pool, $0 included structured garage parking, cheap Santa Clara SVP electricity, and strict no-pets policy (spotless common areas!).</t>
+        </is>
+      </c>
+      <c r="W67" s="3" t="inlineStr">
+        <is>
+          <t>Base 1BR rent starts at $3,400; select an interior-facing unit away from El Camino Real.</t>
+        </is>
+      </c>
+      <c r="X67" s="3" t="inlineStr">
+        <is>
+          <t>3406 El Camino Real, Santa Clara, CA 95051</t>
+        </is>
+      </c>
+      <c r="Y67" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-deck-santa-clara-ca/3x5w42f/</t>
+        </is>
+      </c>
+      <c r="Z67" s="3" t="inlineStr">
+        <is>
+          <t>https://www.deanzaproperties.com/thedeck</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="42" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Graham at The Fields</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Milpitas Corridor</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Trader Joe's On-Site + $0 Free Parking</t>
+        </is>
+      </c>
+      <c r="E68" s="3">
+        <v>2.6</v>
+      </c>
+      <c r="F68" s="3">
+        <v>7</v>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>15m total (5m walk → 5m VTA Orange Line → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H68" s="3">
+        <v>3170</v>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="J68" s="3">
+        <v>3410</v>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>717–1076</t>
+        </is>
+      </c>
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N68" s="3">
+        <v>215</v>
+      </c>
+      <c r="O68" s="3">
+        <v>3385</v>
+      </c>
+      <c r="P68" s="3">
+        <v>3625</v>
+      </c>
+      <c r="Q68" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R68" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S68" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T68" s="3">
+        <v>3.7</v>
+      </c>
+      <c r="U68" s="3" t="inlineStr">
+        <is>
+          <t>Lyon Living (Verified Master-Planned Community (The Fields))</t>
+        </is>
+      </c>
+      <c r="V68" s="3" t="inlineStr">
+        <is>
+          <t>Unlike Turing and Gideon next door, Graham includes your 1st garage parking space FREE ($0/mo) while still giving you Trader Joe's downstairs and a 6-min drive to Cisco!</t>
+        </is>
+      </c>
+      <c r="W68" s="3" t="inlineStr">
+        <is>
+          <t>Strict visitor parking rules; standard Lyon Living move-out cleaning deductions.</t>
+        </is>
+      </c>
+      <c r="X68" s="3" t="inlineStr">
+        <is>
+          <t>1415 McCandless Dr, Milpitas, CA 95035</t>
+        </is>
+      </c>
+      <c r="Y68" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/graham-at-the-fields-milpitas-ca/6xnnf5v/</t>
+        </is>
+      </c>
+      <c r="Z68" s="3" t="inlineStr">
+        <is>
+          <t>https://www.livethefields.com/graham</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="42" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>The Hazelwood Apartments</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Milpitas Corridor</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>720 Sq Ft 1BR at $2,700 + $0 Parking</t>
+        </is>
+      </c>
+      <c r="E69" s="2">
+        <v>4.6</v>
+      </c>
+      <c r="F69" s="2">
+        <v>10</v>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>26m total (3m walk → 18m VTA Bus 66 South → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H69" s="2">
+        <v>2360</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>310–410</t>
+        </is>
+      </c>
+      <c r="J69" s="2">
+        <v>2700</v>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="L69" s="2">
+        <v>0</v>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N69" s="2">
+        <v>200</v>
+      </c>
+      <c r="O69" s="2">
+        <v>2560</v>
+      </c>
+      <c r="P69" s="2">
+        <v>2900</v>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T69" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>Klingbeil Capital Management (Verified Renovated Garden Community)</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>True 720 sq ft 1-Bedroom starting at $2,700/mo (and micro-studios at $2,360) with $0 covered parking, Ecobee central A/C, and in-unit W/D just 9 minutes down I-880 S to Cisco!</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>Studio layout ('The Lily') is micro-sized — opt for the 720 sq ft 1BR ('The Poppy') at $2,700 instead.</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>2021 N Milpitas Blvd, Milpitas, CA 95035</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-hazelwood-milpitas-ca/cv309he/</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thehazelwoodapts.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="42" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Foundry Commons</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Japantown &amp; Downtown</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>4.2★ Studio $2,300 / 1BR $2,850 + 6 Wks Free</t>
+        </is>
+      </c>
+      <c r="E70" s="3">
+        <v>7.9</v>
+      </c>
+      <c r="F70" s="3">
+        <v>15</v>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>31m total (6m walk → 20m VTA Blue Line → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H70" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="J70" s="3">
+        <v>2850</v>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>690–726</t>
+        </is>
+      </c>
+      <c r="L70" s="3">
+        <v>75</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N70" s="3">
+        <v>210</v>
+      </c>
+      <c r="O70" s="3">
+        <v>2585</v>
+      </c>
+      <c r="P70" s="3">
+        <v>3135</v>
+      </c>
+      <c r="Q70" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R70" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S70" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T70" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="U70" s="3" t="inlineStr">
+        <is>
+          <t>Greystar (Verified Institutional Manager (Greystar))</t>
+        </is>
+      </c>
+      <c r="V70" s="3" t="inlineStr">
+        <is>
+          <t>4.2★ Greystar community where BOTH 560 sq ft Studios ($2,300) and 690–726 sq ft 1BRs ($2,850) start well under $3,000 with 6–8 weeks free specials!</t>
+        </is>
+      </c>
+      <c r="W70" s="3" t="inlineStr">
+        <is>
+          <t>Limited street guest parking; industrial/residential fringe south of SJSU.</t>
+        </is>
+      </c>
+      <c r="X70" s="3" t="inlineStr">
+        <is>
+          <t>868 S 5th St, San Jose, CA 95112</t>
+        </is>
+      </c>
+      <c r="Y70" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/foundry-commons-san-jose-ca/v7v04xe/</t>
+        </is>
+      </c>
+      <c r="Z70" s="3" t="inlineStr">
+        <is>
+          <t>https://www.foundrycommonsapts.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="42" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Avalon at Cahill Park</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Midtown &amp; West SJ</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>4.3★ AvalonBay Across from Whole Foods</t>
+        </is>
+      </c>
+      <c r="E71" s="3">
+        <v>6.9</v>
+      </c>
+      <c r="F71" s="3">
+        <v>13</v>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>30m total (4m walk → 21m VTA Green → Blue Line → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J71" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>712–991</t>
+        </is>
+      </c>
+      <c r="L71" s="3">
+        <v>100</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N71" s="3">
+        <v>210</v>
+      </c>
+      <c r="O71" s="3">
+        <v>3410</v>
+      </c>
+      <c r="P71" s="3">
+        <v>3410</v>
+      </c>
+      <c r="Q71" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R71" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S71" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T71" s="3">
+        <v>4.3</v>
+      </c>
+      <c r="U71" s="3" t="inlineStr">
+        <is>
+          <t>AvalonBay Communities (Verified Institutional REIT (AvalonBay))</t>
+        </is>
+      </c>
+      <c r="V71" s="3" t="inlineStr">
+        <is>
+          <t>4.3★ AvalonBay flagship right across from Whole Foods Market, Cahill Park, and Diridon Station with spacious 712–991 sq ft 1BR floor plans.</t>
+        </is>
+      </c>
+      <c r="W71" s="3" t="inlineStr">
+        <is>
+          <t>Caltrain/SAP Center activity nearby; $100/mo parking fee.</t>
+        </is>
+      </c>
+      <c r="X71" s="3" t="inlineStr">
+        <is>
+          <t>754 The Alameda, San Jose, CA 95126</t>
+        </is>
+      </c>
+      <c r="Y71" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/avalon-at-cahill-park-san-jose-ca/1krpwp7/</t>
+        </is>
+      </c>
+      <c r="Z71" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avaloncommunities.com/california/san-jose-apartments/avalon-at-cahill-park/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="42" customHeight="1">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Artis Willow Glen (Silver)</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Midtown &amp; West SJ</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Studio $2,875 / 1BR $2,995 + 6 Wks Free</t>
+        </is>
+      </c>
+      <c r="E72" s="3">
+        <v>7.7</v>
+      </c>
+      <c r="F72" s="3">
+        <v>13</v>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>34m total (5m walk → 24m VTA Green → Blue Line → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H72" s="3">
+        <v>2875</v>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>523–614</t>
+        </is>
+      </c>
+      <c r="J72" s="3">
+        <v>2995</v>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>666–982</t>
+        </is>
+      </c>
+      <c r="L72" s="3">
+        <v>150</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N72" s="3">
+        <v>215</v>
+      </c>
+      <c r="O72" s="3">
+        <v>3240</v>
+      </c>
+      <c r="P72" s="3">
+        <v>3360</v>
+      </c>
+      <c r="Q72" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R72" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S72" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T72" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="U72" s="3" t="inlineStr">
+        <is>
+          <t>Greystar (Verified Institutional Manager (Greystar))</t>
+        </is>
+      </c>
+      <c r="V72" s="3" t="inlineStr">
+        <is>
+          <t>Both Studios ($2,875) and entry 1BRs ($2,995) start under $3,000 right next to Del Monte Park and Los Gatos Creek Trail, plus up to 6 weeks free!</t>
+        </is>
+      </c>
+      <c r="W72" s="3" t="inlineStr">
+        <is>
+          <t>$150/mo garage parking fee; Caltrain tracks run behind the eastern edge of the property.</t>
+        </is>
+      </c>
+      <c r="X72" s="3" t="inlineStr">
+        <is>
+          <t>333 Sunol St, San Jose, CA 95126</t>
+        </is>
+      </c>
+      <c r="Y72" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/artis-willow-glen-san-jose-ca/m0q63fl/</t>
+        </is>
+      </c>
+      <c r="Z72" s="3" t="inlineStr">
+        <is>
+          <t>https://www.silversj.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="42" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>The Maddox Sunnyvale</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale &amp; Campbell</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Sub-$3,000 Sunnyvale Studio + $0 Parking</t>
+        </is>
+      </c>
+      <c r="E73" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="F73" s="2">
+        <v>20</v>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>30m total (3m walk → 22m VTA Bus 56 North → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H73" s="2">
+        <v>2920</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="J73" s="2">
+        <v>3320</v>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>712–733</t>
+        </is>
+      </c>
+      <c r="L73" s="2">
+        <v>0</v>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N73" s="2">
+        <v>205</v>
+      </c>
+      <c r="O73" s="2">
+        <v>3125</v>
+      </c>
+      <c r="P73" s="2">
+        <v>3525</v>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T73" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>IEC Property Services (Verified Market-Rate Community (IEC))</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>Sub-$3,000 Sunnyvale Studio ($2,920) and $3,320 1BR with $0 covered parking, Central A/C, and In-Unit W/D right along Sunnyvale's best dining strip.</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>Late-1980s building framing (renovated interiors); pick a courtyard unit away from El Camino Real.</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>874 E El Camino Real, Sunnyvale, CA 94087</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-maddox-sunnyvale-sunnyvale-ca/h4yw0y1/</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.maddoxsunnyvaleapartments.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="42" customHeight="1">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>481 on Mathilda</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Sunnyvale &amp; Campbell</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>4.2★ 3 Blocks to Sunnyvale Whole Foods &amp; AMC</t>
+        </is>
+      </c>
+      <c r="E74" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="F74" s="3">
+        <v>18</v>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>30m total (3m walk → 22m VTA Bus 55 North → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H74" s="3">
+        <v>3250</v>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>557–650</t>
+        </is>
+      </c>
+      <c r="J74" s="3">
+        <v>3495</v>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>745–791</t>
+        </is>
+      </c>
+      <c r="L74" s="3">
+        <v>75</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N74" s="3">
+        <v>215</v>
+      </c>
+      <c r="O74" s="3">
+        <v>3540</v>
+      </c>
+      <c r="P74" s="3">
+        <v>3785</v>
+      </c>
+      <c r="Q74" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R74" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S74" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T74" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="U74" s="3" t="inlineStr">
+        <is>
+          <t>Greystar (Verified Institutional Manager (Greystar))</t>
+        </is>
+      </c>
+      <c r="V74" s="3" t="inlineStr">
+        <is>
+          <t>4.2★ Greystar luxury just 3 blocks south of Downtown Sunnyvale's Whole Foods, Target, AMC dine-in theater, and Murphy Ave restaurants!</t>
+        </is>
+      </c>
+      <c r="W74" s="3" t="inlineStr">
+        <is>
+          <t>Mathilda Ave commuter traffic during rush hour; $75/mo parking fee.</t>
+        </is>
+      </c>
+      <c r="X74" s="3" t="inlineStr">
+        <is>
+          <t>481 S Mathilda Ave, Sunnyvale, CA 94086</t>
+        </is>
+      </c>
+      <c r="Y74" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/481-on-mathilda-sunnyvale-ca/tx88gtb/</t>
+        </is>
+      </c>
+      <c r="Z74" s="3" t="inlineStr">
+        <is>
+          <t>https://www.481onmathilda.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="42" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Naya Apartments</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Sunnyvale &amp; Campbell</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>4.3★ 2-Story Gym + Straight Hwy 237 Commute</t>
+        </is>
+      </c>
+      <c r="E75" s="3">
+        <v>9.8</v>
+      </c>
+      <c r="F75" s="3">
+        <v>16</v>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>31m total (3m walk → 23m VTA Rapid 523 → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J75" s="3">
+        <v>3490</v>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>694–765</t>
+        </is>
+      </c>
+      <c r="L75" s="3">
+        <v>75</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N75" s="3">
+        <v>215</v>
+      </c>
+      <c r="O75" s="3">
+        <v>3780</v>
+      </c>
+      <c r="P75" s="3">
+        <v>3780</v>
+      </c>
+      <c r="Q75" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R75" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S75" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T75" s="3">
+        <v>4.3</v>
+      </c>
+      <c r="U75" s="3" t="inlineStr">
+        <is>
+          <t>Greystar (Verified Institutional Manager (Greystar))</t>
+        </is>
+      </c>
+      <c r="V75" s="3" t="inlineStr">
+        <is>
+          <t>4.3★ Greystar building with one of the best 2-story apartment gyms in Sunnyvale, strong soundproofing, and a straight 14-min commute on Hwy 237 E to Cisco.</t>
+        </is>
+      </c>
+      <c r="W75" s="3" t="inlineStr">
+        <is>
+          <t>Sits at the $3,490 base budget cap before applying lease specials; $75/mo underground parking.</t>
+        </is>
+      </c>
+      <c r="X75" s="3" t="inlineStr">
+        <is>
+          <t>1095 W El Camino Real, Sunnyvale, CA 94087</t>
+        </is>
+      </c>
+      <c r="Y75" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/naya-sunnyvale-ca/prdh34v/</t>
+        </is>
+      </c>
+      <c r="Z75" s="3" t="inlineStr">
+        <is>
+          <t>https://www.liveatnaya.com/</t>
         </is>
       </c>
     </row>
@@ -20589,6 +24955,814 @@
         </is>
       </c>
     </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Nantucket Apartments</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Santa Clara (SVP Utility)</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>2.5 Mi to Cisco + SVP Power + $0 Park</t>
+        </is>
+      </c>
+      <c r="E25" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="F25" s="3">
+        <v>9</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>17m total (5m walk → 7m VTA Orange Line → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J25" s="3">
+        <v>3150</v>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>735–856</t>
+        </is>
+      </c>
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Silicon Valley Power (~$0.18/kWh — 60% cheaper!)</t>
+        </is>
+      </c>
+      <c r="N25" s="3">
+        <v>120</v>
+      </c>
+      <c r="O25" s="3">
+        <v>3270</v>
+      </c>
+      <c r="P25" s="3">
+        <v>3270</v>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T25" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>AMC (Apartment Management Consultants) (Verified Market-Rate Garden Community)</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>Only 2.5 miles down Tasman Dr to Cisco HQ; includes $0 covered parking and 60% cheaper Santa Clara Silicon Valley Power electricity (~$120/mo summer A/C savings).</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>Levi's Stadium event days can bring temporary traffic along Great America Pkwy; older 1980s exterior framing (interiors renovated).</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>1600 Nantucket Cir, Santa Clara, CA 95054</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/nantucket-santa-clara-ca/fjmjsrv/</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nantucket-apartments.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Park Central Apartments</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Santa Clara (SVP Utility)</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>8 Weeks Free (-$515/mo) + SVP + $0 Park</t>
+        </is>
+      </c>
+      <c r="E26" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F26" s="3">
+        <v>11</v>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>29m total (6m walk → 18m VTA Bus 60 North → VTA Blue Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J26" s="3">
+        <v>3350</v>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>662–740</t>
+        </is>
+      </c>
+      <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Silicon Valley Power (~$0.18/kWh — 60% cheaper!)</t>
+        </is>
+      </c>
+      <c r="N26" s="3">
+        <v>125</v>
+      </c>
+      <c r="O26" s="3">
+        <v>3475</v>
+      </c>
+      <c r="P26" s="3">
+        <v>3475</v>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T26" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>Prometheus Real Estate Group (Verified Institutional Manager (Prometheus))</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>Up to 8 weeks free rent (-$515/mo credit) drops net effective rent to ~$2,835/mo, plus $0 free parking and cheap Santa Clara SVP electricity!</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>Higher base sticker rent after year-1 concession expires; visitor parking requires permit.</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>1050 Benton St, Santa Clara, CA 95050</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/park-central-santa-clara-ca/9hj8bj5/</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/apartments/ca/santa-clara/park-central/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Hearth Apartments</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Santa Clara (SVP Utility)</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Steps to Central Park + SVP Power + $0 Park</t>
+        </is>
+      </c>
+      <c r="E27" s="2">
+        <v>6.4</v>
+      </c>
+      <c r="F27" s="2">
+        <v>13</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>29m total (3m walk → 21m VTA Bus 57 North → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J27" s="2">
+        <v>3450</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>686–751</t>
+        </is>
+      </c>
+      <c r="L27" s="2">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Silicon Valley Power (~$0.18/kWh — 60% cheaper!)</t>
+        </is>
+      </c>
+      <c r="N27" s="2">
+        <v>125</v>
+      </c>
+      <c r="O27" s="2">
+        <v>3575</v>
+      </c>
+      <c r="P27" s="2">
+        <v>3575</v>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T27" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>Prometheus Real Estate Group (Verified Institutional Manager (Prometheus))</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Walkable to Santa Clara Central Park, library, and Safeway; includes $0 free parking, cheap SVP electricity, and up to 3 weeks free.</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>Near the $3,450 top of the budget range before applying the 3-weeks-free special.</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>2870 Kaiser Dr, Santa Clara, CA 95051</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/hearth-santa-clara-ca/jmgnhs6/</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/apartments/ca/santa-clara/hearth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>The Benton</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Santa Clara (SVP Utility)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2021 Rooftop Saltwater Pool + SVP Power</t>
+        </is>
+      </c>
+      <c r="E28" s="2">
+        <v>4.9</v>
+      </c>
+      <c r="F28" s="2">
+        <v>10</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>28m total (5m walk → 18m VTA Bus 60 North → VTA Blue Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J28" s="2">
+        <v>3475</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>755–913</t>
+        </is>
+      </c>
+      <c r="L28" s="2">
+        <v>100</v>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Silicon Valley Power (~$0.18/kWh — 60% cheaper!)</t>
+        </is>
+      </c>
+      <c r="N28" s="2">
+        <v>130</v>
+      </c>
+      <c r="O28" s="2">
+        <v>3705</v>
+      </c>
+      <c r="P28" s="2">
+        <v>3705</v>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T28" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>Prometheus Real Estate Group (Verified 2021 Luxury Build (Prometheus))</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Newer 2021 luxury construction with large 755–913 sq ft 1BR layouts, rooftop saltwater pool, and cheap Santa Clara SVP electric rates.</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>Sits at the top of the $3,500 base budget cap with $100/mo parking; request an interior courtyard unit away from El Camino Real.</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>588 El Camino Real, Santa Clara, CA 95050</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-benton-santa-clara-ca/dxh36kl/</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/apartments/ca/santa-clara/the-benton/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>The Luxe Apartments</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Santa Clara (SVP Utility)</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>1BR at $2,595 + SVP Power + $0 Garage</t>
+        </is>
+      </c>
+      <c r="E29" s="3">
+        <v>8.4</v>
+      </c>
+      <c r="F29" s="3">
+        <v>16</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>32m total (3m walk → 24m VTA Bus 57 North → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H29" s="3">
+        <v>2395</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>450–520</t>
+        </is>
+      </c>
+      <c r="J29" s="3">
+        <v>2595</v>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>650–720</t>
+        </is>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Silicon Valley Power (~$0.18/kWh — 60% cheaper!)</t>
+        </is>
+      </c>
+      <c r="N29" s="3">
+        <v>115</v>
+      </c>
+      <c r="O29" s="3">
+        <v>2510</v>
+      </c>
+      <c r="P29" s="3">
+        <v>2710</v>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T29" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>Spieker Companies (Verified Market-Rate Community (Spieker))</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>Rare sub-$2,600 1BR ($2,595) and $2,395 Studio in Santa Clara with $0 underground garage parking, In-Unit W/D, Central A/C, and cheap SVP electricity!</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>14-minute commute up Lawrence Expy -&gt; Hwy 237 E to Cisco; finishes are clean and functional rather than ultra-high-rise luxury.</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>3301 Homestead Rd, Santa Clara, CA 95051</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-luxe-santa-clara-ca/58bdlkm/</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.theluxeapartments.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Boardwalk at The Lakes</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Santa Clara (SVP Utility)</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>$2,650 Studio + Waterfront Lagoons + SVP</t>
+        </is>
+      </c>
+      <c r="E30" s="2">
+        <v>7.1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>14</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>30m total (4m walk → 21m VTA Bus 57 North → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H30" s="2">
+        <v>2650</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="J30" s="2">
+        <v>3295</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>700–750</t>
+        </is>
+      </c>
+      <c r="L30" s="2">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Silicon Valley Power (~$0.18/kWh — 60% cheaper!)</t>
+        </is>
+      </c>
+      <c r="N30" s="2">
+        <v>120</v>
+      </c>
+      <c r="O30" s="2">
+        <v>2770</v>
+      </c>
+      <c r="P30" s="2">
+        <v>3415</v>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T30" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>Prometheus Real Estate Group (Verified Institutional Manager (Prometheus))</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Unique waterfront lagoon setting with studios at $2,650, $0 included parking, responsive Prometheus maintenance, and cheap Santa Clara SVP electricity.</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>Resident ducks around the waterways leave droppings on paths; studios are compact.</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>3770 Flora Vista Ave, Santa Clara, CA 95051</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/boardwalk-santa-clara-ca/gx12z2y/</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/apartments/ca/santa-clara/boardwalk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>The Deck Apartment Homes</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Santa Clara (SVP Utility)</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>2024 Build + Rooftop Pool + SVP + $0 Park</t>
+        </is>
+      </c>
+      <c r="E31" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="F31" s="3">
+        <v>13</v>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>29m total (3m walk → 21m VTA Bus 57 North → VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J31" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>728–780</t>
+        </is>
+      </c>
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Silicon Valley Power (~$0.18/kWh — 60% cheaper!)</t>
+        </is>
+      </c>
+      <c r="N31" s="3">
+        <v>120</v>
+      </c>
+      <c r="O31" s="3">
+        <v>3520</v>
+      </c>
+      <c r="P31" s="3">
+        <v>3520</v>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T31" s="3">
+        <v>4.1</v>
+      </c>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>De Anza Properties (Verified 2024 Luxury Build (De Anza Properties))</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>Brand-new 2024 build with a rooftop heated pool, $0 included structured garage parking, cheap Santa Clara SVP electricity, and strict no-pets policy (spotless common areas!).</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>Base 1BR rent starts at $3,400; select an interior-facing unit away from El Camino Real.</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>3406 El Camino Real, Santa Clara, CA 95051</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-deck-santa-clara-ca/3x5w42f/</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.deanzaproperties.com/thedeck</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/San_Jose_Apartments_Tracker.xlsx
+++ b/San_Jose_Apartments_Tracker.xlsx
@@ -13547,6 +13547,1732 @@
         </is>
       </c>
     </row>
+    <row r="118" ht="42" customHeight="1">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>Aya Apartments</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>Milpitas Corridor</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>Walk to Warm Springs BART + $0 Garage</t>
+        </is>
+      </c>
+      <c r="E118" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="F118" s="3">
+        <v>14</v>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>24m total (4m walk → 15m BART Southbound → Milpitas VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H118" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I118" s="3" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="J118" s="3">
+        <v>3256</v>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>678–775</t>
+        </is>
+      </c>
+      <c r="L118" s="3">
+        <v>0</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N118" s="3">
+        <v>210</v>
+      </c>
+      <c r="O118" s="3">
+        <v>3310</v>
+      </c>
+      <c r="P118" s="3">
+        <v>3466</v>
+      </c>
+      <c r="Q118" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R118" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S118" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T118" s="3">
+        <v>4.1</v>
+      </c>
+      <c r="U118" s="3" t="inlineStr">
+        <is>
+          <t>MG Properties (Verified Market-Rate Luxury Community (2022 Build))</t>
+        </is>
+      </c>
+      <c r="V118" s="3" t="inlineStr">
+        <is>
+          <t>Walk 4 minutes to Warm Springs BART (1 stop to Milpitas BART -&gt; VTA Orange Line to Cisco Way) or hop straight down I-880 S; includes $0 free garage parking and huge 655 sq ft studios.</t>
+        </is>
+      </c>
+      <c r="W118" s="3" t="inlineStr">
+        <is>
+          <t>Limited immediate late-night restaurants on surrounding Warm Springs Innovation District blocks; occasional BART track dust on outward-facing balconies.</t>
+        </is>
+      </c>
+      <c r="X118" s="3" t="inlineStr">
+        <is>
+          <t>45147 Lopes Rd, Fremont, CA 94538</t>
+        </is>
+      </c>
+      <c r="Y118" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/aya-apartments-fremont-ca/wxez1gh/</t>
+        </is>
+      </c>
+      <c r="Z118" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayaapts.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="42" customHeight="1">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>Leya Apartments</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Milpitas Corridor</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>4.4★ Brand-New + $2,950 Studio + $0 Park</t>
+        </is>
+      </c>
+      <c r="E119" s="3">
+        <v>8.7</v>
+      </c>
+      <c r="F119" s="3">
+        <v>14</v>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>26m total (6m walk → 15m BART Southbound → Milpitas VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H119" s="3">
+        <v>2950</v>
+      </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="J119" s="3">
+        <v>3130</v>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>690–780</t>
+        </is>
+      </c>
+      <c r="L119" s="3">
+        <v>0</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N119" s="3">
+        <v>210</v>
+      </c>
+      <c r="O119" s="3">
+        <v>3160</v>
+      </c>
+      <c r="P119" s="3">
+        <v>3340</v>
+      </c>
+      <c r="Q119" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R119" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S119" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T119" s="3">
+        <v>4.4</v>
+      </c>
+      <c r="U119" s="3" t="inlineStr">
+        <is>
+          <t>Quarterra Multifamily (Verified Market-Rate Luxury Community (2023 Build))</t>
+        </is>
+      </c>
+      <c r="V119" s="3" t="inlineStr">
+        <is>
+          <t>4.4★ rating! Brand-new luxury finishes with Studios under $3,000 ($2,950), $0 included garage parking, up to 6 weeks free, and walkable to Warm Springs BART.</t>
+        </is>
+      </c>
+      <c r="W119" s="3" t="inlineStr">
+        <is>
+          <t>Occasional early-morning commercial/construction truck noise along Innovation Way.</t>
+        </is>
+      </c>
+      <c r="X119" s="3" t="inlineStr">
+        <is>
+          <t>3301 Innovation Way, Fremont, CA 94538</t>
+        </is>
+      </c>
+      <c r="Y119" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/leya-fremont-ca/mkzbh5l/</t>
+        </is>
+      </c>
+      <c r="Z119" s="3" t="inlineStr">
+        <is>
+          <t>https://www.liveleya.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="42" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>eaves Fremont</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Milpitas Corridor</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>AvalonBay 1BR at $2,850 + $0 Parking</t>
+        </is>
+      </c>
+      <c r="E120" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="F120" s="2">
+        <v>16</v>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>31m total (8m walk → 18m Bus 251 / Bike to Warm Springs BART → Milpitas VTA Orange Line → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J120" s="2">
+        <v>2850</v>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>701–901</t>
+        </is>
+      </c>
+      <c r="L120" s="2">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N120" s="2">
+        <v>205</v>
+      </c>
+      <c r="O120" s="2">
+        <v>3055</v>
+      </c>
+      <c r="P120" s="2">
+        <v>3055</v>
+      </c>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R120" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S120" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T120" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="U120" s="2" t="inlineStr">
+        <is>
+          <t>AvalonBay Communities (Verified Market-Rate Garden Community (REIT))</t>
+        </is>
+      </c>
+      <c r="V120" s="2" t="inlineStr">
+        <is>
+          <t>True sub-$2,900 1-Bedroom ($2,850 for 701–901 sq ft) managed by AvalonBay with $0 included parking in quiet, safe Warm Springs / Mission San Jose.</t>
+        </is>
+      </c>
+      <c r="W120" s="2" t="inlineStr">
+        <is>
+          <t>Older 1980s garden-style wood framing; open guest parking fills up in the evening.</t>
+        </is>
+      </c>
+      <c r="X120" s="2" t="inlineStr">
+        <is>
+          <t>231 Woodcreek Cmn, Fremont, CA 94539</t>
+        </is>
+      </c>
+      <c r="Y120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/eaves-fremont-fremont-ca/w4ek4pk/</t>
+        </is>
+      </c>
+      <c r="Z120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avaloncommunities.com/california/fremont-apartments/eaves-fremont/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="42" customHeight="1">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>The Tolman</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Milpitas Corridor</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>4.4★ Luxury 1BR $2,695 / Studio $2,420 ($0 Park)</t>
+        </is>
+      </c>
+      <c r="E121" s="3">
+        <v>12.7</v>
+      </c>
+      <c r="F121" s="3">
+        <v>19</v>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>32m total (6m walk → 21m BART Orange/Green Line → Milpitas VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H121" s="3">
+        <v>2420</v>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="J121" s="3">
+        <v>2695</v>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>688–748</t>
+        </is>
+      </c>
+      <c r="L121" s="3">
+        <v>0</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N121" s="3">
+        <v>205</v>
+      </c>
+      <c r="O121" s="3">
+        <v>2625</v>
+      </c>
+      <c r="P121" s="3">
+        <v>2900</v>
+      </c>
+      <c r="Q121" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R121" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S121" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T121" s="3">
+        <v>4.4</v>
+      </c>
+      <c r="U121" s="3" t="inlineStr">
+        <is>
+          <t>Woodmont Real Estate Services (Verified Market-Rate Luxury Community)</t>
+        </is>
+      </c>
+      <c r="V121" s="3" t="inlineStr">
+        <is>
+          <t>Phenomenal luxury value just north of Warm Springs: 4.4★ rating, Studios at $2,420 and 1BRs at $2,695 with $0 free garage parking and direct BART access to Milpitas/VTA!</t>
+        </is>
+      </c>
+      <c r="W121" s="3" t="inlineStr">
+        <is>
+          <t>Slightly longer 13-mile I-880 S drive to Cisco compared to Warm Springs/Milpitas; standard arterial traffic on Fremont Blvd.</t>
+        </is>
+      </c>
+      <c r="X121" s="3" t="inlineStr">
+        <is>
+          <t>39176 Fremont Blvd, Fremont, CA 94538</t>
+        </is>
+      </c>
+      <c r="Y121" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-tolman-fremont-ca/4flaayc/</t>
+        </is>
+      </c>
+      <c r="Z121" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thetolmanapts.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="42" customHeight="1">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>The Martin at CityLine</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Sunnyvale &amp; Campbell</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>4.3★ Brand-New Downtown Sunnyvale CityLine</t>
+        </is>
+      </c>
+      <c r="E122" s="3">
+        <v>8.4</v>
+      </c>
+      <c r="F122" s="3">
+        <v>14</v>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>29m total (3m walk → 21m VTA Bus 55 North → VTA Orange Line East to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H122" s="3">
+        <v>3325</v>
+      </c>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>524–536</t>
+        </is>
+      </c>
+      <c r="J122" s="3">
+        <v>3495</v>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>694–958</t>
+        </is>
+      </c>
+      <c r="L122" s="3">
+        <v>100</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N122" s="3">
+        <v>215</v>
+      </c>
+      <c r="O122" s="3">
+        <v>3640</v>
+      </c>
+      <c r="P122" s="3">
+        <v>3810</v>
+      </c>
+      <c r="Q122" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R122" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S122" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T122" s="3">
+        <v>4.3</v>
+      </c>
+      <c r="U122" s="3" t="inlineStr">
+        <is>
+          <t>Sares-Regis Group (Verified Market-Rate Luxury High-Rise (2024 Build))</t>
+        </is>
+      </c>
+      <c r="V122" s="3" t="inlineStr">
+        <is>
+          <t>4.3★ brand-new 2024 luxury building right in the heart of CityLine Sunnyvale — Whole Foods, Target, AMC Theater, and 30+ Murphy Ave restaurants are literally downstairs!</t>
+        </is>
+      </c>
+      <c r="W122" s="3" t="inlineStr">
+        <is>
+          <t>Unbundled $100/mo garage parking; 1BRs quickly climb above $3,500 (target the 536 sq ft Studios with 4 weeks free).</t>
+        </is>
+      </c>
+      <c r="X122" s="3" t="inlineStr">
+        <is>
+          <t>240 S Taaffe St, Sunnyvale, CA 94086</t>
+        </is>
+      </c>
+      <c r="Y122" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-martin-sunnyvale-ca-94086/enp0vt6/</t>
+        </is>
+      </c>
+      <c r="Z122" s="3" t="inlineStr">
+        <is>
+          <t>https://livethemartin.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="42" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Arioso Apartments</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale &amp; Campbell</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Across from Apple Park + $0 Underground Garage</t>
+        </is>
+      </c>
+      <c r="E123" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="F123" s="2">
+        <v>19</v>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>35m total (3m walk → 27m VTA Bus 56 North → VTA Orange Line East to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J123" s="2">
+        <v>3359</v>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>534–829</t>
+        </is>
+      </c>
+      <c r="L123" s="2">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N123" s="2">
+        <v>210</v>
+      </c>
+      <c r="O123" s="2">
+        <v>3569</v>
+      </c>
+      <c r="P123" s="2">
+        <v>3569</v>
+      </c>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S123" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T123" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="U123" s="2" t="inlineStr">
+        <is>
+          <t>Willow Bridge Property Company (Verified Market-Rate Luxury Community)</t>
+        </is>
+      </c>
+      <c r="V123" s="2" t="inlineStr">
+        <is>
+          <t>Prime Cupertino address directly across from Apple Park and walkable to Main Street Cupertino dining, with $0 included underground garage parking.</t>
+        </is>
+      </c>
+      <c r="W123" s="2" t="inlineStr">
+        <is>
+          <t>Limited visitor parking spaces; annual lease renewal increases.</t>
+        </is>
+      </c>
+      <c r="X123" s="2" t="inlineStr">
+        <is>
+          <t>19608 Pruneridge Ave, Cupertino, CA 95014</t>
+        </is>
+      </c>
+      <c r="Y123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/arioso-cupertino-ca/dxEaLh0/</t>
+        </is>
+      </c>
+      <c r="Z123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ariosoapartments.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="42" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>City Gate at Cupertino</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale &amp; Campbell</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Walk to Main St Cupertino + $0 Garage</t>
+        </is>
+      </c>
+      <c r="E124" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="F124" s="2">
+        <v>19</v>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>36m total (3m walk → 28m VTA Bus 56 North → VTA Orange Line East to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J124" s="2">
+        <v>3241</v>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>728–774</t>
+        </is>
+      </c>
+      <c r="L124" s="2">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N124" s="2">
+        <v>210</v>
+      </c>
+      <c r="O124" s="2">
+        <v>3451</v>
+      </c>
+      <c r="P124" s="2">
+        <v>3451</v>
+      </c>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S124" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T124" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="U124" s="2" t="inlineStr">
+        <is>
+          <t>Equity Residential (Verified Market-Rate Community (REIT))</t>
+        </is>
+      </c>
+      <c r="V124" s="2" t="inlineStr">
+        <is>
+          <t>Steps from Main Street Cupertino restaurants, Philz Coffee, and Target; spacious 728–774 sq ft 1BRs with $0 included underground parking.</t>
+        </is>
+      </c>
+      <c r="W124" s="2" t="inlineStr">
+        <is>
+          <t>Stevens Creek Blvd traffic noise on south-facing balconies (choose a courtyard-facing unit).</t>
+        </is>
+      </c>
+      <c r="X124" s="2" t="inlineStr">
+        <is>
+          <t>5608 Stevens Creek Blvd, Cupertino, CA 95014</t>
+        </is>
+      </c>
+      <c r="Y124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/city-gate-at-cupertino-cupertino-ca/l17q0p2/</t>
+        </is>
+      </c>
+      <c r="Z124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.equityapartments.com/san-francisco-bay-area/cupertino/city-gate-at-cupertino-apartments</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="42" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>The Villages at Cupertino</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale &amp; Campbell</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>27-Acre Cupertino Park Setting + $0 Park</t>
+        </is>
+      </c>
+      <c r="E125" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="F125" s="2">
+        <v>22</v>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>37m total (5m walk → 27m VTA Bus 55 North → VTA Orange Line East to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H125" s="2">
+        <v>3212</v>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="J125" s="2">
+        <v>3495</v>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>680–730</t>
+        </is>
+      </c>
+      <c r="L125" s="2">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N125" s="2">
+        <v>205</v>
+      </c>
+      <c r="O125" s="2">
+        <v>3417</v>
+      </c>
+      <c r="P125" s="2">
+        <v>3700</v>
+      </c>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S125" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T125" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="U125" s="2" t="inlineStr">
+        <is>
+          <t>Prometheus Real Estate Group (Verified Market-Rate Garden Community)</t>
+        </is>
+      </c>
+      <c r="V125" s="2" t="inlineStr">
+        <is>
+          <t>Massive 27-acre green park setting in Cupertino with tennis courts, Prometheus management, $0 included parking, and up to 3 weeks free.</t>
+        </is>
+      </c>
+      <c r="W125" s="2" t="inlineStr">
+        <is>
+          <t>Older vintage wood-frame construction (request an upper-floor unit to avoid upstairs footsteps).</t>
+        </is>
+      </c>
+      <c r="X125" s="2" t="inlineStr">
+        <is>
+          <t>20875 Valley Green Dr, Cupertino, CA 95014</t>
+        </is>
+      </c>
+      <c r="Y125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/villages-at-cupertino-cupertino-ca/xc_7t2j/</t>
+        </is>
+      </c>
+      <c r="Z125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.prometheusapartments.com/ca/cupertino-apartments/villages-at-cupertino/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="42" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Americana Apartments</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale &amp; Campbell</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Direct Hwy 237 East Shot + VTA Orange Line</t>
+        </is>
+      </c>
+      <c r="E126" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="F126" s="2">
+        <v>14</v>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>33m total (7m walk → 21m VTA Orange Line → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J126" s="2">
+        <v>3243</v>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>610–750</t>
+        </is>
+      </c>
+      <c r="L126" s="2">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N126" s="2">
+        <v>210</v>
+      </c>
+      <c r="O126" s="2">
+        <v>3453</v>
+      </c>
+      <c r="P126" s="2">
+        <v>3453</v>
+      </c>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R126" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S126" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T126" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="U126" s="2" t="inlineStr">
+        <is>
+          <t>Prometheus Real Estate Group (Verified Market-Rate Garden Community)</t>
+        </is>
+      </c>
+      <c r="V126" s="2" t="inlineStr">
+        <is>
+          <t>Sits right at the Hwy 237 / Hwy 85 junction for a straight shot east on Hwy 237 to Cisco Way, plus direct VTA Orange Line access and $0 parking.</t>
+        </is>
+      </c>
+      <c r="W126" s="2" t="inlineStr">
+        <is>
+          <t>Carport parking rather than fully enclosed underground garage; standard Prometheus move-out cleaning deductions.</t>
+        </is>
+      </c>
+      <c r="X126" s="2" t="inlineStr">
+        <is>
+          <t>707 Continental Cir, Mountain View, CA 94040</t>
+        </is>
+      </c>
+      <c r="Y126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/americana-apartments-mountain-view-ca/peO12Fv/</t>
+        </is>
+      </c>
+      <c r="Z126" s="2" t="inlineStr">
+        <is>
+          <t>https://liveatamericana.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="42" customHeight="1">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>300 Railway</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Sunnyvale &amp; Campbell</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>4.4★ Walkable Downtown Campbell + $0 Garage</t>
+        </is>
+      </c>
+      <c r="E127" s="3">
+        <v>11.8</v>
+      </c>
+      <c r="F127" s="3">
+        <v>17</v>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>36m total (2m walk → 29m VTA Green Line → VTA Blue Line North to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H127" s="3">
+        <v>2975</v>
+      </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="J127" s="3">
+        <v>3450</v>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>680–745</t>
+        </is>
+      </c>
+      <c r="L127" s="3">
+        <v>0</v>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N127" s="3">
+        <v>205</v>
+      </c>
+      <c r="O127" s="3">
+        <v>3180</v>
+      </c>
+      <c r="P127" s="3">
+        <v>3655</v>
+      </c>
+      <c r="Q127" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R127" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S127" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T127" s="3">
+        <v>4.4</v>
+      </c>
+      <c r="U127" s="3" t="inlineStr">
+        <is>
+          <t>St. Anton Multifamily (Verified Market-Rate Community)</t>
+        </is>
+      </c>
+      <c r="V127" s="3" t="inlineStr">
+        <is>
+          <t>4.4★ rating right in walkable Downtown Campbell! Step out your door to Campbell Ave cafes, Los Gatos Creek Trail, and Downtown Campbell VTA Light Rail, with $0 free garage parking.</t>
+        </is>
+      </c>
+      <c r="W127" s="3" t="inlineStr">
+        <is>
+          <t>Studios are cozy (441 sq ft); light rail bell audible when windows are open.</t>
+        </is>
+      </c>
+      <c r="X127" s="3" t="inlineStr">
+        <is>
+          <t>300 Railway Ave, Campbell, CA 95008</t>
+        </is>
+      </c>
+      <c r="Y127" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/300-railway-campbell-ca/bj6kr9b/</t>
+        </is>
+      </c>
+      <c r="Z127" s="3" t="inlineStr">
+        <is>
+          <t>https://www.300railway.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="42" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>The Parc at Pruneyard</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale &amp; Campbell</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Across from Campbell Pruneyard Trader Joe's</t>
+        </is>
+      </c>
+      <c r="E128" s="2">
+        <v>12.4</v>
+      </c>
+      <c r="F128" s="2">
+        <v>20</v>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>40m total (6m walk → 29m VTA Green Line → VTA Blue Line North to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J128" s="2">
+        <v>3397</v>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="L128" s="2">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N128" s="2">
+        <v>210</v>
+      </c>
+      <c r="O128" s="2">
+        <v>3607</v>
+      </c>
+      <c r="P128" s="2">
+        <v>3607</v>
+      </c>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S128" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T128" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="U128" s="2" t="inlineStr">
+        <is>
+          <t>Essex Property Trust (Verified Market-Rate Community (REIT))</t>
+        </is>
+      </c>
+      <c r="V128" s="2" t="inlineStr">
+        <is>
+          <t>Walk across the street to The Pruneyard (Trader Joe's, Mendocino Farms, Rock Bottom, CineArts) and Los Gatos Creek Trail; $0 included parking.</t>
+        </is>
+      </c>
+      <c r="W128" s="2" t="inlineStr">
+        <is>
+          <t>Older wood-frame floors can transmit upstairs footsteps; tight evening guest parking.</t>
+        </is>
+      </c>
+      <c r="X128" s="2" t="inlineStr">
+        <is>
+          <t>225 Union Ave, Campbell, CA 95008</t>
+        </is>
+      </c>
+      <c r="Y128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-parc-at-pruneyard-campbell-ca/h07w213/</t>
+        </is>
+      </c>
+      <c r="Z128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.essexapartmenthomes.com/apartments/campbell/the-parc-at-pruneyard</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="42" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>The Franciscan Apartments</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale &amp; Campbell</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>4.0★ Renovated Campbell 1BR ($3,072 + $0 Park)</t>
+        </is>
+      </c>
+      <c r="E129" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="F129" s="2">
+        <v>19</v>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>41m total (9m walk → 27m VTA Green Line → VTA Blue Line North to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J129" s="2">
+        <v>3072</v>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="L129" s="2">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N129" s="2">
+        <v>205</v>
+      </c>
+      <c r="O129" s="2">
+        <v>3277</v>
+      </c>
+      <c r="P129" s="2">
+        <v>3277</v>
+      </c>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S129" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T129" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="U129" s="2" t="inlineStr">
+        <is>
+          <t>Greystar (Verified Market-Rate Community)</t>
+        </is>
+      </c>
+      <c r="V129" s="2" t="inlineStr">
+        <is>
+          <t>4.0★ Greystar-managed community in Campbell with renovated quartz kitchen islands, $0 included parking, and easy Hwy 17 / I-880 access.</t>
+        </is>
+      </c>
+      <c r="W129" s="2" t="inlineStr">
+        <is>
+          <t>Limited parking for a 2nd vehicle; occasional daytime exterior maintenance noise.</t>
+        </is>
+      </c>
+      <c r="X129" s="2" t="inlineStr">
+        <is>
+          <t>601 Almarida Dr, Campbell, CA 95008</t>
+        </is>
+      </c>
+      <c r="Y129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-franciscan-campbell-ca/w0gt9ql/</t>
+        </is>
+      </c>
+      <c r="Z129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.liveatfranciscan.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="42" customHeight="1">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>Maxwell at Bascom</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Midtown &amp; West SJ</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>4.5★ 2024 Build + Up to 8 Weeks Free</t>
+        </is>
+      </c>
+      <c r="E130" s="3">
+        <v>11.5</v>
+      </c>
+      <c r="F130" s="3">
+        <v>17</v>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>36m total (4m walk → 27m VTA Green Line → VTA Blue Line North to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H130" s="3">
+        <v>2911</v>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>466–587</t>
+        </is>
+      </c>
+      <c r="J130" s="3">
+        <v>3304</v>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>607–649</t>
+        </is>
+      </c>
+      <c r="L130" s="3">
+        <v>125</v>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N130" s="3">
+        <v>215</v>
+      </c>
+      <c r="O130" s="3">
+        <v>3251</v>
+      </c>
+      <c r="P130" s="3">
+        <v>3644</v>
+      </c>
+      <c r="Q130" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R130" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S130" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T130" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="U130" s="3" t="inlineStr">
+        <is>
+          <t>Greystar (Verified Market-Rate Luxury Community (2024 Build))</t>
+        </is>
+      </c>
+      <c r="V130" s="3" t="inlineStr">
+        <is>
+          <t>4.5★ brand-new 2024 luxury construction between Willow Glen and Campbell Pruneyard with Studios under $3,000 ($2,911) and up to 8 weeks free!</t>
+        </is>
+      </c>
+      <c r="W130" s="3" t="inlineStr">
+        <is>
+          <t>Unbundled $125/mo garage parking; request an interior courtyard unit away from S. Bascom Ave.</t>
+        </is>
+      </c>
+      <c r="X130" s="3" t="inlineStr">
+        <is>
+          <t>1350 S Bascom Ave, San Jose, CA 95128</t>
+        </is>
+      </c>
+      <c r="Y130" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/maxwell-at-bascom-san-jose-ca/163qzv7/</t>
+        </is>
+      </c>
+      <c r="Z130" s="3" t="inlineStr">
+        <is>
+          <t>https://maxwellatbascom.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="42" customHeight="1">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>La Terraza Apartments</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Midtown &amp; West SJ</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>4.5★ Huge 825–910 Sq Ft 1BR + $0 Garage</t>
+        </is>
+      </c>
+      <c r="E131" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="F131" s="3">
+        <v>17</v>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>35m total (3m walk → 27m VTA Bus 57 North → VTA Orange Line East to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J131" s="3">
+        <v>3231</v>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>825–910</t>
+        </is>
+      </c>
+      <c r="L131" s="3">
+        <v>0</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N131" s="3">
+        <v>215</v>
+      </c>
+      <c r="O131" s="3">
+        <v>3446</v>
+      </c>
+      <c r="P131" s="3">
+        <v>3446</v>
+      </c>
+      <c r="Q131" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R131" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S131" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T131" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="U131" s="3" t="inlineStr">
+        <is>
+          <t>Greystar (Verified Market-Rate Luxury Community)</t>
+        </is>
+      </c>
+      <c r="V131" s="3" t="inlineStr">
+        <is>
+          <t>4.5★ resident rating! Huge 825–910 sq ft 1BR floor plans with $0 included garage parking, 4–6 weeks free, and instant I-280 access near Santana Row &amp; Mitsuwa.</t>
+        </is>
+      </c>
+      <c r="W131" s="3" t="inlineStr">
+        <is>
+          <t>Weekend guest parking fills up quickly; Saratoga Ave rush-hour traffic near I-280.</t>
+        </is>
+      </c>
+      <c r="X131" s="3" t="inlineStr">
+        <is>
+          <t>470 Saratoga Ave, San Jose, CA 95129</t>
+        </is>
+      </c>
+      <c r="Y131" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/la-terraza-san-jose-ca/wucpje8/</t>
+        </is>
+      </c>
+      <c r="Z131" s="3" t="inlineStr">
+        <is>
+          <t>https://www.liveatlaterraza.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="42" customHeight="1">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>Avalon Willow Glen</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>Midtown &amp; West SJ</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>4.2★ AvalonBay 1BR at $2,770 + Direct VTA Blue Line</t>
+        </is>
+      </c>
+      <c r="E132" s="3">
+        <v>11.3</v>
+      </c>
+      <c r="F132" s="3">
+        <v>18</v>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>37m total (5m walk → 27m VTA Blue Line → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J132" s="3">
+        <v>2770</v>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>726–814</t>
+        </is>
+      </c>
+      <c r="L132" s="3">
+        <v>0</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N132" s="3">
+        <v>205</v>
+      </c>
+      <c r="O132" s="3">
+        <v>2975</v>
+      </c>
+      <c r="P132" s="3">
+        <v>2975</v>
+      </c>
+      <c r="Q132" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R132" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S132" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T132" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="U132" s="3" t="inlineStr">
+        <is>
+          <t>AvalonBay Communities (Verified Market-Rate Community (REIT))</t>
+        </is>
+      </c>
+      <c r="V132" s="3" t="inlineStr">
+        <is>
+          <t>4.2★ AvalonBay community where a spacious 726–814 sq ft 1BR starts at just $2,770/mo with $0 free parking AND walks directly to the VTA Blue Line (no transfers to Cisco Way!).</t>
+        </is>
+      </c>
+      <c r="W132" s="3" t="inlineStr">
+        <is>
+          <t>Garden walk-up buildings do not have elevators; unassigned surface spots fill up late at night.</t>
+        </is>
+      </c>
+      <c r="X132" s="3" t="inlineStr">
+        <is>
+          <t>3200 Rubino Dr, San Jose, CA 95125</t>
+        </is>
+      </c>
+      <c r="Y132" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/avalon-willow-glen-san-jose-ca/4zfygh5/</t>
+        </is>
+      </c>
+      <c r="Z132" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avaloncommunities.com/california/san-jose-apartments/avalon-willow-glen/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -22161,6 +23887,1038 @@
       <c r="Z75" s="3" t="inlineStr">
         <is>
           <t>https://www.liveatnaya.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="42" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Aya Apartments</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Milpitas Corridor</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Walk to Warm Springs BART + $0 Garage</t>
+        </is>
+      </c>
+      <c r="E76" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="F76" s="3">
+        <v>14</v>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>24m total (4m walk → 15m BART Southbound → Milpitas VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H76" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="J76" s="3">
+        <v>3256</v>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>678–775</t>
+        </is>
+      </c>
+      <c r="L76" s="3">
+        <v>0</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N76" s="3">
+        <v>210</v>
+      </c>
+      <c r="O76" s="3">
+        <v>3310</v>
+      </c>
+      <c r="P76" s="3">
+        <v>3466</v>
+      </c>
+      <c r="Q76" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R76" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S76" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T76" s="3">
+        <v>4.1</v>
+      </c>
+      <c r="U76" s="3" t="inlineStr">
+        <is>
+          <t>MG Properties (Verified Market-Rate Luxury Community (2022 Build))</t>
+        </is>
+      </c>
+      <c r="V76" s="3" t="inlineStr">
+        <is>
+          <t>Walk 4 minutes to Warm Springs BART (1 stop to Milpitas BART -&gt; VTA Orange Line to Cisco Way) or hop straight down I-880 S; includes $0 free garage parking and huge 655 sq ft studios.</t>
+        </is>
+      </c>
+      <c r="W76" s="3" t="inlineStr">
+        <is>
+          <t>Limited immediate late-night restaurants on surrounding Warm Springs Innovation District blocks; occasional BART track dust on outward-facing balconies.</t>
+        </is>
+      </c>
+      <c r="X76" s="3" t="inlineStr">
+        <is>
+          <t>45147 Lopes Rd, Fremont, CA 94538</t>
+        </is>
+      </c>
+      <c r="Y76" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/aya-apartments-fremont-ca/wxez1gh/</t>
+        </is>
+      </c>
+      <c r="Z76" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ayaapts.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="42" customHeight="1">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Leya Apartments</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Milpitas Corridor</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>4.4★ Brand-New + $2,950 Studio + $0 Park</t>
+        </is>
+      </c>
+      <c r="E77" s="3">
+        <v>8.7</v>
+      </c>
+      <c r="F77" s="3">
+        <v>14</v>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>26m total (6m walk → 15m BART Southbound → Milpitas VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H77" s="3">
+        <v>2950</v>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="J77" s="3">
+        <v>3130</v>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>690–780</t>
+        </is>
+      </c>
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N77" s="3">
+        <v>210</v>
+      </c>
+      <c r="O77" s="3">
+        <v>3160</v>
+      </c>
+      <c r="P77" s="3">
+        <v>3340</v>
+      </c>
+      <c r="Q77" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R77" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S77" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T77" s="3">
+        <v>4.4</v>
+      </c>
+      <c r="U77" s="3" t="inlineStr">
+        <is>
+          <t>Quarterra Multifamily (Verified Market-Rate Luxury Community (2023 Build))</t>
+        </is>
+      </c>
+      <c r="V77" s="3" t="inlineStr">
+        <is>
+          <t>4.4★ rating! Brand-new luxury finishes with Studios under $3,000 ($2,950), $0 included garage parking, up to 6 weeks free, and walkable to Warm Springs BART.</t>
+        </is>
+      </c>
+      <c r="W77" s="3" t="inlineStr">
+        <is>
+          <t>Occasional early-morning commercial/construction truck noise along Innovation Way.</t>
+        </is>
+      </c>
+      <c r="X77" s="3" t="inlineStr">
+        <is>
+          <t>3301 Innovation Way, Fremont, CA 94538</t>
+        </is>
+      </c>
+      <c r="Y77" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/leya-fremont-ca/mkzbh5l/</t>
+        </is>
+      </c>
+      <c r="Z77" s="3" t="inlineStr">
+        <is>
+          <t>https://www.liveleya.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="42" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Strong Contender</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>eaves Fremont</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Milpitas Corridor</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>AvalonBay 1BR at $2,850 + $0 Parking</t>
+        </is>
+      </c>
+      <c r="E78" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="F78" s="2">
+        <v>16</v>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>31m total (8m walk → 18m Bus 251 / Bike to Warm Springs BART → Milpitas VTA Orange Line → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J78" s="2">
+        <v>2850</v>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>701–901</t>
+        </is>
+      </c>
+      <c r="L78" s="2">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N78" s="2">
+        <v>205</v>
+      </c>
+      <c r="O78" s="2">
+        <v>3055</v>
+      </c>
+      <c r="P78" s="2">
+        <v>3055</v>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T78" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>AvalonBay Communities (Verified Market-Rate Garden Community (REIT))</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>True sub-$2,900 1-Bedroom ($2,850 for 701–901 sq ft) managed by AvalonBay with $0 included parking in quiet, safe Warm Springs / Mission San Jose.</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>Older 1980s garden-style wood framing; open guest parking fills up in the evening.</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>231 Woodcreek Cmn, Fremont, CA 94539</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/eaves-fremont-fremont-ca/w4ek4pk/</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avaloncommunities.com/california/fremont-apartments/eaves-fremont/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="42" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>The Tolman</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Milpitas Corridor</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>4.4★ Luxury 1BR $2,695 / Studio $2,420 ($0 Park)</t>
+        </is>
+      </c>
+      <c r="E79" s="3">
+        <v>12.7</v>
+      </c>
+      <c r="F79" s="3">
+        <v>19</v>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>32m total (6m walk → 21m BART Orange/Green Line → Milpitas VTA Orange Line to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H79" s="3">
+        <v>2420</v>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="J79" s="3">
+        <v>2695</v>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>688–748</t>
+        </is>
+      </c>
+      <c r="L79" s="3">
+        <v>0</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N79" s="3">
+        <v>205</v>
+      </c>
+      <c r="O79" s="3">
+        <v>2625</v>
+      </c>
+      <c r="P79" s="3">
+        <v>2900</v>
+      </c>
+      <c r="Q79" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R79" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S79" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T79" s="3">
+        <v>4.4</v>
+      </c>
+      <c r="U79" s="3" t="inlineStr">
+        <is>
+          <t>Woodmont Real Estate Services (Verified Market-Rate Luxury Community)</t>
+        </is>
+      </c>
+      <c r="V79" s="3" t="inlineStr">
+        <is>
+          <t>Phenomenal luxury value just north of Warm Springs: 4.4★ rating, Studios at $2,420 and 1BRs at $2,695 with $0 free garage parking and direct BART access to Milpitas/VTA!</t>
+        </is>
+      </c>
+      <c r="W79" s="3" t="inlineStr">
+        <is>
+          <t>Slightly longer 13-mile I-880 S drive to Cisco compared to Warm Springs/Milpitas; standard arterial traffic on Fremont Blvd.</t>
+        </is>
+      </c>
+      <c r="X79" s="3" t="inlineStr">
+        <is>
+          <t>39176 Fremont Blvd, Fremont, CA 94538</t>
+        </is>
+      </c>
+      <c r="Y79" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-tolman-fremont-ca/4flaayc/</t>
+        </is>
+      </c>
+      <c r="Z79" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thetolmanapts.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="42" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>The Martin at CityLine</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Sunnyvale &amp; Campbell</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>4.3★ Brand-New Downtown Sunnyvale CityLine</t>
+        </is>
+      </c>
+      <c r="E80" s="3">
+        <v>8.4</v>
+      </c>
+      <c r="F80" s="3">
+        <v>14</v>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>29m total (3m walk → 21m VTA Bus 55 North → VTA Orange Line East to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H80" s="3">
+        <v>3325</v>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>524–536</t>
+        </is>
+      </c>
+      <c r="J80" s="3">
+        <v>3495</v>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>694–958</t>
+        </is>
+      </c>
+      <c r="L80" s="3">
+        <v>100</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N80" s="3">
+        <v>215</v>
+      </c>
+      <c r="O80" s="3">
+        <v>3640</v>
+      </c>
+      <c r="P80" s="3">
+        <v>3810</v>
+      </c>
+      <c r="Q80" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R80" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S80" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T80" s="3">
+        <v>4.3</v>
+      </c>
+      <c r="U80" s="3" t="inlineStr">
+        <is>
+          <t>Sares-Regis Group (Verified Market-Rate Luxury High-Rise (2024 Build))</t>
+        </is>
+      </c>
+      <c r="V80" s="3" t="inlineStr">
+        <is>
+          <t>4.3★ brand-new 2024 luxury building right in the heart of CityLine Sunnyvale — Whole Foods, Target, AMC Theater, and 30+ Murphy Ave restaurants are literally downstairs!</t>
+        </is>
+      </c>
+      <c r="W80" s="3" t="inlineStr">
+        <is>
+          <t>Unbundled $100/mo garage parking; 1BRs quickly climb above $3,500 (target the 536 sq ft Studios with 4 weeks free).</t>
+        </is>
+      </c>
+      <c r="X80" s="3" t="inlineStr">
+        <is>
+          <t>240 S Taaffe St, Sunnyvale, CA 94086</t>
+        </is>
+      </c>
+      <c r="Y80" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-martin-sunnyvale-ca-94086/enp0vt6/</t>
+        </is>
+      </c>
+      <c r="Z80" s="3" t="inlineStr">
+        <is>
+          <t>https://livethemartin.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="42" customHeight="1">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>300 Railway</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Sunnyvale &amp; Campbell</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>4.4★ Walkable Downtown Campbell + $0 Garage</t>
+        </is>
+      </c>
+      <c r="E81" s="3">
+        <v>11.8</v>
+      </c>
+      <c r="F81" s="3">
+        <v>17</v>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>36m total (2m walk → 29m VTA Green Line → VTA Blue Line North to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H81" s="3">
+        <v>2975</v>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="J81" s="3">
+        <v>3450</v>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>680–745</t>
+        </is>
+      </c>
+      <c r="L81" s="3">
+        <v>0</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N81" s="3">
+        <v>205</v>
+      </c>
+      <c r="O81" s="3">
+        <v>3180</v>
+      </c>
+      <c r="P81" s="3">
+        <v>3655</v>
+      </c>
+      <c r="Q81" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R81" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S81" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T81" s="3">
+        <v>4.4</v>
+      </c>
+      <c r="U81" s="3" t="inlineStr">
+        <is>
+          <t>St. Anton Multifamily (Verified Market-Rate Community)</t>
+        </is>
+      </c>
+      <c r="V81" s="3" t="inlineStr">
+        <is>
+          <t>4.4★ rating right in walkable Downtown Campbell! Step out your door to Campbell Ave cafes, Los Gatos Creek Trail, and Downtown Campbell VTA Light Rail, with $0 free garage parking.</t>
+        </is>
+      </c>
+      <c r="W81" s="3" t="inlineStr">
+        <is>
+          <t>Studios are cozy (441 sq ft); light rail bell audible when windows are open.</t>
+        </is>
+      </c>
+      <c r="X81" s="3" t="inlineStr">
+        <is>
+          <t>300 Railway Ave, Campbell, CA 95008</t>
+        </is>
+      </c>
+      <c r="Y81" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/300-railway-campbell-ca/bj6kr9b/</t>
+        </is>
+      </c>
+      <c r="Z81" s="3" t="inlineStr">
+        <is>
+          <t>https://www.300railway.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="42" customHeight="1">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Maxwell at Bascom</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Midtown &amp; West SJ</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>4.5★ 2024 Build + Up to 8 Weeks Free</t>
+        </is>
+      </c>
+      <c r="E82" s="3">
+        <v>11.5</v>
+      </c>
+      <c r="F82" s="3">
+        <v>17</v>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>36m total (4m walk → 27m VTA Green Line → VTA Blue Line North to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H82" s="3">
+        <v>2911</v>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>466–587</t>
+        </is>
+      </c>
+      <c r="J82" s="3">
+        <v>3304</v>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>607–649</t>
+        </is>
+      </c>
+      <c r="L82" s="3">
+        <v>125</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N82" s="3">
+        <v>215</v>
+      </c>
+      <c r="O82" s="3">
+        <v>3251</v>
+      </c>
+      <c r="P82" s="3">
+        <v>3644</v>
+      </c>
+      <c r="Q82" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R82" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S82" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T82" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="U82" s="3" t="inlineStr">
+        <is>
+          <t>Greystar (Verified Market-Rate Luxury Community (2024 Build))</t>
+        </is>
+      </c>
+      <c r="V82" s="3" t="inlineStr">
+        <is>
+          <t>4.5★ brand-new 2024 luxury construction between Willow Glen and Campbell Pruneyard with Studios under $3,000 ($2,911) and up to 8 weeks free!</t>
+        </is>
+      </c>
+      <c r="W82" s="3" t="inlineStr">
+        <is>
+          <t>Unbundled $125/mo garage parking; request an interior courtyard unit away from S. Bascom Ave.</t>
+        </is>
+      </c>
+      <c r="X82" s="3" t="inlineStr">
+        <is>
+          <t>1350 S Bascom Ave, San Jose, CA 95128</t>
+        </is>
+      </c>
+      <c r="Y82" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/maxwell-at-bascom-san-jose-ca/163qzv7/</t>
+        </is>
+      </c>
+      <c r="Z82" s="3" t="inlineStr">
+        <is>
+          <t>https://maxwellatbascom.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="42" customHeight="1">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>La Terraza Apartments</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Midtown &amp; West SJ</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>4.5★ Huge 825–910 Sq Ft 1BR + $0 Garage</t>
+        </is>
+      </c>
+      <c r="E83" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="F83" s="3">
+        <v>17</v>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>35m total (3m walk → 27m VTA Bus 57 North → VTA Orange Line East to Cisco Way → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J83" s="3">
+        <v>3231</v>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>825–910</t>
+        </is>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N83" s="3">
+        <v>215</v>
+      </c>
+      <c r="O83" s="3">
+        <v>3446</v>
+      </c>
+      <c r="P83" s="3">
+        <v>3446</v>
+      </c>
+      <c r="Q83" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R83" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S83" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T83" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="U83" s="3" t="inlineStr">
+        <is>
+          <t>Greystar (Verified Market-Rate Luxury Community)</t>
+        </is>
+      </c>
+      <c r="V83" s="3" t="inlineStr">
+        <is>
+          <t>4.5★ resident rating! Huge 825–910 sq ft 1BR floor plans with $0 included garage parking, 4–6 weeks free, and instant I-280 access near Santana Row &amp; Mitsuwa.</t>
+        </is>
+      </c>
+      <c r="W83" s="3" t="inlineStr">
+        <is>
+          <t>Weekend guest parking fills up quickly; Saratoga Ave rush-hour traffic near I-280.</t>
+        </is>
+      </c>
+      <c r="X83" s="3" t="inlineStr">
+        <is>
+          <t>470 Saratoga Ave, San Jose, CA 95129</t>
+        </is>
+      </c>
+      <c r="Y83" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/la-terraza-san-jose-ca/wucpje8/</t>
+        </is>
+      </c>
+      <c r="Z83" s="3" t="inlineStr">
+        <is>
+          <t>https://www.liveatlaterraza.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="42" customHeight="1">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Avalon Willow Glen</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Midtown &amp; West SJ</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>4.2★ AvalonBay 1BR at $2,770 + Direct VTA Blue Line</t>
+        </is>
+      </c>
+      <c r="E84" s="3">
+        <v>11.3</v>
+      </c>
+      <c r="F84" s="3">
+        <v>18</v>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>37m total (5m walk → 27m VTA Blue Line → 5m walk)</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J84" s="3">
+        <v>2770</v>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>726–814</t>
+        </is>
+      </c>
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>PG&amp;E (~$0.44/kWh)</t>
+        </is>
+      </c>
+      <c r="N84" s="3">
+        <v>205</v>
+      </c>
+      <c r="O84" s="3">
+        <v>2975</v>
+      </c>
+      <c r="P84" s="3">
+        <v>2975</v>
+      </c>
+      <c r="Q84" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R84" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S84" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T84" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="U84" s="3" t="inlineStr">
+        <is>
+          <t>AvalonBay Communities (Verified Market-Rate Community (REIT))</t>
+        </is>
+      </c>
+      <c r="V84" s="3" t="inlineStr">
+        <is>
+          <t>4.2★ AvalonBay community where a spacious 726–814 sq ft 1BR starts at just $2,770/mo with $0 free parking AND walks directly to the VTA Blue Line (no transfers to Cisco Way!).</t>
+        </is>
+      </c>
+      <c r="W84" s="3" t="inlineStr">
+        <is>
+          <t>Garden walk-up buildings do not have elevators; unassigned surface spots fill up late at night.</t>
+        </is>
+      </c>
+      <c r="X84" s="3" t="inlineStr">
+        <is>
+          <t>3200 Rubino Dr, San Jose, CA 95125</t>
+        </is>
+      </c>
+      <c r="Y84" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/avalon-willow-glen-san-jose-ca/4zfygh5/</t>
+        </is>
+      </c>
+      <c r="Z84" s="3" t="inlineStr">
+        <is>
+          <t>https://www.avaloncommunities.com/california/san-jose-apartments/avalon-willow-glen/</t>
         </is>
       </c>
     </row>
